--- a/output/version3/test/15-10/MARL/IL/RL-RL/(RL+RL) test results.xlsx
+++ b/output/version3/test/15-10/MARL/IL/RL-RL/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C2" t="n">
-        <v>555</v>
+        <v>573</v>
       </c>
       <c r="D2" t="n">
-        <v>572</v>
+        <v>714</v>
       </c>
       <c r="E2" t="n">
-        <v>545</v>
+        <v>706</v>
       </c>
       <c r="F2" t="n">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="G2" t="n">
-        <v>668</v>
+        <v>569</v>
       </c>
       <c r="H2" t="n">
-        <v>524</v>
+        <v>622</v>
       </c>
       <c r="I2" t="n">
-        <v>807</v>
+        <v>793</v>
       </c>
       <c r="J2" t="n">
-        <v>857</v>
+        <v>576</v>
       </c>
       <c r="K2" t="n">
-        <v>518</v>
+        <v>701</v>
       </c>
       <c r="L2" t="n">
-        <v>628</v>
+        <v>648.4</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>710</v>
+        <v>638</v>
       </c>
       <c r="C3" t="n">
-        <v>644</v>
+        <v>598</v>
       </c>
       <c r="D3" t="n">
         <v>634</v>
       </c>
       <c r="E3" t="n">
-        <v>624</v>
+        <v>594</v>
       </c>
       <c r="F3" t="n">
-        <v>684</v>
+        <v>666</v>
       </c>
       <c r="G3" t="n">
-        <v>642</v>
+        <v>579</v>
       </c>
       <c r="H3" t="n">
-        <v>667</v>
+        <v>578</v>
       </c>
       <c r="I3" t="n">
-        <v>650</v>
+        <v>671</v>
       </c>
       <c r="J3" t="n">
-        <v>652</v>
+        <v>623</v>
       </c>
       <c r="K3" t="n">
-        <v>648</v>
+        <v>723</v>
       </c>
       <c r="L3" t="n">
-        <v>655.5</v>
+        <v>630.4</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>655</v>
+        <v>573</v>
       </c>
       <c r="C4" t="n">
-        <v>709</v>
+        <v>684</v>
       </c>
       <c r="D4" t="n">
-        <v>578</v>
+        <v>620</v>
       </c>
       <c r="E4" t="n">
+        <v>662</v>
+      </c>
+      <c r="F4" t="n">
+        <v>660</v>
+      </c>
+      <c r="G4" t="n">
+        <v>595</v>
+      </c>
+      <c r="H4" t="n">
+        <v>585</v>
+      </c>
+      <c r="I4" t="n">
+        <v>785</v>
+      </c>
+      <c r="J4" t="n">
+        <v>557</v>
+      </c>
+      <c r="K4" t="n">
         <v>589</v>
       </c>
-      <c r="F4" t="n">
-        <v>652</v>
-      </c>
-      <c r="G4" t="n">
-        <v>593</v>
-      </c>
-      <c r="H4" t="n">
-        <v>677</v>
-      </c>
-      <c r="I4" t="n">
-        <v>644</v>
-      </c>
-      <c r="J4" t="n">
-        <v>749</v>
-      </c>
-      <c r="K4" t="n">
-        <v>634</v>
-      </c>
       <c r="L4" t="n">
-        <v>648</v>
+        <v>631</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>639</v>
+        <v>660</v>
       </c>
       <c r="C5" t="n">
-        <v>614</v>
+        <v>686</v>
       </c>
       <c r="D5" t="n">
-        <v>668</v>
+        <v>630</v>
       </c>
       <c r="E5" t="n">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="F5" t="n">
-        <v>631</v>
+        <v>770</v>
       </c>
       <c r="G5" t="n">
-        <v>623</v>
+        <v>649</v>
       </c>
       <c r="H5" t="n">
-        <v>760</v>
+        <v>620</v>
       </c>
       <c r="I5" t="n">
-        <v>663</v>
+        <v>696</v>
       </c>
       <c r="J5" t="n">
-        <v>644</v>
+        <v>586</v>
       </c>
       <c r="K5" t="n">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="L5" t="n">
-        <v>657.4</v>
+        <v>662.6</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>598</v>
+        <v>532</v>
       </c>
       <c r="C6" t="n">
-        <v>686</v>
+        <v>620</v>
       </c>
       <c r="D6" t="n">
-        <v>670</v>
+        <v>637</v>
       </c>
       <c r="E6" t="n">
-        <v>546</v>
+        <v>613</v>
       </c>
       <c r="F6" t="n">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="G6" t="n">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="H6" t="n">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="I6" t="n">
-        <v>631</v>
+        <v>605</v>
       </c>
       <c r="J6" t="n">
-        <v>648</v>
+        <v>614</v>
       </c>
       <c r="K6" t="n">
-        <v>568</v>
+        <v>683</v>
       </c>
       <c r="L6" t="n">
-        <v>617</v>
+        <v>611.7</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>664</v>
+        <v>538</v>
       </c>
       <c r="C7" t="n">
-        <v>543</v>
+        <v>687</v>
       </c>
       <c r="D7" t="n">
-        <v>582</v>
+        <v>640</v>
       </c>
       <c r="E7" t="n">
-        <v>678</v>
+        <v>551</v>
       </c>
       <c r="F7" t="n">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="G7" t="n">
-        <v>544</v>
+        <v>581</v>
       </c>
       <c r="H7" t="n">
-        <v>627</v>
+        <v>671</v>
       </c>
       <c r="I7" t="n">
-        <v>544</v>
+        <v>636</v>
       </c>
       <c r="J7" t="n">
-        <v>568</v>
+        <v>640</v>
       </c>
       <c r="K7" t="n">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="L7" t="n">
-        <v>595.5</v>
+        <v>613.6</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>642</v>
+        <v>684</v>
       </c>
       <c r="C8" t="n">
-        <v>589</v>
+        <v>605</v>
       </c>
       <c r="D8" t="n">
-        <v>531</v>
+        <v>714</v>
       </c>
       <c r="E8" t="n">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="F8" t="n">
-        <v>564</v>
+        <v>675</v>
       </c>
       <c r="G8" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="H8" t="n">
-        <v>597</v>
+        <v>582</v>
       </c>
       <c r="I8" t="n">
-        <v>603</v>
+        <v>649</v>
       </c>
       <c r="J8" t="n">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="K8" t="n">
-        <v>544</v>
+        <v>701</v>
       </c>
       <c r="L8" t="n">
-        <v>588.4</v>
+        <v>641.6</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C9" t="n">
-        <v>588</v>
+        <v>627</v>
       </c>
       <c r="D9" t="n">
-        <v>617</v>
+        <v>555</v>
       </c>
       <c r="E9" t="n">
-        <v>730</v>
+        <v>539</v>
       </c>
       <c r="F9" t="n">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="G9" t="n">
-        <v>609</v>
+        <v>568</v>
       </c>
       <c r="H9" t="n">
-        <v>654</v>
+        <v>607</v>
       </c>
       <c r="I9" t="n">
-        <v>619</v>
+        <v>714</v>
       </c>
       <c r="J9" t="n">
         <v>604</v>
       </c>
       <c r="K9" t="n">
-        <v>586</v>
+        <v>606</v>
       </c>
       <c r="L9" t="n">
-        <v>610</v>
+        <v>592.7</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>794</v>
+        <v>654</v>
       </c>
       <c r="C10" t="n">
-        <v>724</v>
+        <v>827</v>
       </c>
       <c r="D10" t="n">
-        <v>681</v>
+        <v>719</v>
       </c>
       <c r="E10" t="n">
-        <v>712</v>
+        <v>775</v>
       </c>
       <c r="F10" t="n">
-        <v>764</v>
+        <v>840</v>
       </c>
       <c r="G10" t="n">
-        <v>746</v>
+        <v>723</v>
       </c>
       <c r="H10" t="n">
-        <v>855</v>
+        <v>830</v>
       </c>
       <c r="I10" t="n">
-        <v>626</v>
+        <v>829</v>
       </c>
       <c r="J10" t="n">
-        <v>745</v>
+        <v>660</v>
       </c>
       <c r="K10" t="n">
-        <v>733</v>
+        <v>687</v>
       </c>
       <c r="L10" t="n">
-        <v>738</v>
+        <v>754.4</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>623</v>
+        <v>649</v>
       </c>
       <c r="C11" t="n">
-        <v>625</v>
+        <v>791</v>
       </c>
       <c r="D11" t="n">
-        <v>613</v>
+        <v>674</v>
       </c>
       <c r="E11" t="n">
-        <v>699</v>
+        <v>671</v>
       </c>
       <c r="F11" t="n">
-        <v>601</v>
+        <v>640</v>
       </c>
       <c r="G11" t="n">
-        <v>581</v>
+        <v>608</v>
       </c>
       <c r="H11" t="n">
-        <v>648</v>
+        <v>787</v>
       </c>
       <c r="I11" t="n">
-        <v>627</v>
+        <v>669</v>
       </c>
       <c r="J11" t="n">
-        <v>609</v>
+        <v>593</v>
       </c>
       <c r="K11" t="n">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="L11" t="n">
-        <v>625.2</v>
+        <v>670.3</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>633</v>
+        <v>666</v>
       </c>
       <c r="C12" t="n">
-        <v>666</v>
+        <v>598</v>
       </c>
       <c r="D12" t="n">
-        <v>728</v>
+        <v>700</v>
       </c>
       <c r="E12" t="n">
-        <v>632</v>
+        <v>665</v>
       </c>
       <c r="F12" t="n">
-        <v>693</v>
+        <v>667</v>
       </c>
       <c r="G12" t="n">
-        <v>652</v>
+        <v>598</v>
       </c>
       <c r="H12" t="n">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="I12" t="n">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="J12" t="n">
-        <v>666</v>
+        <v>692</v>
       </c>
       <c r="K12" t="n">
-        <v>644</v>
+        <v>574</v>
       </c>
       <c r="L12" t="n">
-        <v>664.1</v>
+        <v>646.9</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>581</v>
+        <v>829</v>
       </c>
       <c r="C13" t="n">
-        <v>648</v>
+        <v>917</v>
       </c>
       <c r="D13" t="n">
-        <v>733</v>
+        <v>778</v>
       </c>
       <c r="E13" t="n">
-        <v>691</v>
+        <v>819</v>
       </c>
       <c r="F13" t="n">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="G13" t="n">
-        <v>901</v>
+        <v>842</v>
       </c>
       <c r="H13" t="n">
-        <v>609</v>
+        <v>702</v>
       </c>
       <c r="I13" t="n">
-        <v>732</v>
+        <v>798</v>
       </c>
       <c r="J13" t="n">
-        <v>623</v>
+        <v>720</v>
       </c>
       <c r="K13" t="n">
-        <v>711</v>
+        <v>751</v>
       </c>
       <c r="L13" t="n">
-        <v>701.9</v>
+        <v>794.9</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>650</v>
+        <v>671</v>
       </c>
       <c r="C14" t="n">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="D14" t="n">
-        <v>774</v>
+        <v>698</v>
       </c>
       <c r="E14" t="n">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="F14" t="n">
-        <v>708</v>
+        <v>742</v>
       </c>
       <c r="G14" t="n">
-        <v>649</v>
+        <v>689</v>
       </c>
       <c r="H14" t="n">
-        <v>802</v>
+        <v>718</v>
       </c>
       <c r="I14" t="n">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="J14" t="n">
-        <v>747</v>
+        <v>688</v>
       </c>
       <c r="K14" t="n">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="L14" t="n">
-        <v>715.4</v>
+        <v>700.4</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>672</v>
+        <v>737</v>
       </c>
       <c r="C15" t="n">
-        <v>695</v>
+        <v>681</v>
       </c>
       <c r="D15" t="n">
-        <v>752</v>
+        <v>673</v>
       </c>
       <c r="E15" t="n">
-        <v>768</v>
+        <v>656</v>
       </c>
       <c r="F15" t="n">
-        <v>698</v>
+        <v>718</v>
       </c>
       <c r="G15" t="n">
-        <v>754</v>
+        <v>666</v>
       </c>
       <c r="H15" t="n">
-        <v>711</v>
+        <v>685</v>
       </c>
       <c r="I15" t="n">
-        <v>700</v>
+        <v>643</v>
       </c>
       <c r="J15" t="n">
-        <v>663</v>
+        <v>772</v>
       </c>
       <c r="K15" t="n">
-        <v>664</v>
+        <v>807</v>
       </c>
       <c r="L15" t="n">
-        <v>707.7</v>
+        <v>703.8</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>701</v>
+        <v>711</v>
       </c>
       <c r="C16" t="n">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="D16" t="n">
-        <v>748</v>
+        <v>739</v>
       </c>
       <c r="E16" t="n">
-        <v>593</v>
+        <v>764</v>
       </c>
       <c r="F16" t="n">
-        <v>629</v>
+        <v>639</v>
       </c>
       <c r="G16" t="n">
-        <v>712</v>
+        <v>649</v>
       </c>
       <c r="H16" t="n">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="I16" t="n">
-        <v>624</v>
+        <v>640</v>
       </c>
       <c r="J16" t="n">
-        <v>637</v>
+        <v>599</v>
       </c>
       <c r="K16" t="n">
-        <v>652</v>
+        <v>552</v>
       </c>
       <c r="L16" t="n">
-        <v>660.8</v>
+        <v>657.8</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="C17" t="n">
-        <v>697</v>
+        <v>661</v>
       </c>
       <c r="D17" t="n">
-        <v>635</v>
+        <v>604</v>
       </c>
       <c r="E17" t="n">
-        <v>661</v>
+        <v>588</v>
       </c>
       <c r="F17" t="n">
-        <v>598</v>
+        <v>573</v>
       </c>
       <c r="G17" t="n">
-        <v>581</v>
+        <v>613</v>
       </c>
       <c r="H17" t="n">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="I17" t="n">
-        <v>608</v>
+        <v>578</v>
       </c>
       <c r="J17" t="n">
-        <v>641</v>
+        <v>618</v>
       </c>
       <c r="K17" t="n">
-        <v>671</v>
+        <v>654</v>
       </c>
       <c r="L17" t="n">
-        <v>638.2</v>
+        <v>616.2</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>632</v>
+        <v>741</v>
       </c>
       <c r="C18" t="n">
-        <v>639</v>
+        <v>696</v>
       </c>
       <c r="D18" t="n">
-        <v>720</v>
+        <v>597</v>
       </c>
       <c r="E18" t="n">
-        <v>691</v>
+        <v>647</v>
       </c>
       <c r="F18" t="n">
-        <v>636</v>
+        <v>785</v>
       </c>
       <c r="G18" t="n">
-        <v>677</v>
+        <v>660</v>
       </c>
       <c r="H18" t="n">
-        <v>726</v>
+        <v>747</v>
       </c>
       <c r="I18" t="n">
-        <v>596</v>
+        <v>693</v>
       </c>
       <c r="J18" t="n">
-        <v>719</v>
+        <v>709</v>
       </c>
       <c r="K18" t="n">
-        <v>605</v>
+        <v>643</v>
       </c>
       <c r="L18" t="n">
-        <v>664.1</v>
+        <v>691.8</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>683</v>
+        <v>702</v>
       </c>
       <c r="C19" t="n">
-        <v>652</v>
+        <v>710</v>
       </c>
       <c r="D19" t="n">
-        <v>689</v>
+        <v>713</v>
       </c>
       <c r="E19" t="n">
-        <v>642</v>
+        <v>604</v>
       </c>
       <c r="F19" t="n">
-        <v>721</v>
+        <v>780</v>
       </c>
       <c r="G19" t="n">
-        <v>630</v>
+        <v>615</v>
       </c>
       <c r="H19" t="n">
-        <v>644</v>
+        <v>699</v>
       </c>
       <c r="I19" t="n">
-        <v>687</v>
+        <v>646</v>
       </c>
       <c r="J19" t="n">
-        <v>681</v>
+        <v>661</v>
       </c>
       <c r="K19" t="n">
-        <v>710</v>
+        <v>654</v>
       </c>
       <c r="L19" t="n">
-        <v>673.9</v>
+        <v>678.4</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>1017</v>
+        <v>752</v>
       </c>
       <c r="C20" t="n">
-        <v>706</v>
+        <v>871</v>
       </c>
       <c r="D20" t="n">
-        <v>786</v>
+        <v>724</v>
       </c>
       <c r="E20" t="n">
-        <v>800</v>
+        <v>746</v>
       </c>
       <c r="F20" t="n">
+        <v>782</v>
+      </c>
+      <c r="G20" t="n">
         <v>768</v>
       </c>
-      <c r="G20" t="n">
-        <v>766</v>
-      </c>
       <c r="H20" t="n">
-        <v>806</v>
+        <v>773</v>
       </c>
       <c r="I20" t="n">
-        <v>739</v>
+        <v>615</v>
       </c>
       <c r="J20" t="n">
-        <v>704</v>
+        <v>754</v>
       </c>
       <c r="K20" t="n">
-        <v>681</v>
+        <v>835</v>
       </c>
       <c r="L20" t="n">
-        <v>777.3</v>
+        <v>762</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="C21" t="n">
+        <v>761</v>
+      </c>
+      <c r="D21" t="n">
+        <v>751</v>
+      </c>
+      <c r="E21" t="n">
+        <v>608</v>
+      </c>
+      <c r="F21" t="n">
+        <v>763</v>
+      </c>
+      <c r="G21" t="n">
         <v>698</v>
       </c>
-      <c r="D21" t="n">
-        <v>618</v>
-      </c>
-      <c r="E21" t="n">
-        <v>664</v>
-      </c>
-      <c r="F21" t="n">
-        <v>692</v>
-      </c>
-      <c r="G21" t="n">
-        <v>611</v>
-      </c>
       <c r="H21" t="n">
-        <v>585</v>
+        <v>807</v>
       </c>
       <c r="I21" t="n">
-        <v>755</v>
+        <v>783</v>
       </c>
       <c r="J21" t="n">
-        <v>658</v>
+        <v>647</v>
       </c>
       <c r="K21" t="n">
-        <v>719</v>
+        <v>647</v>
       </c>
       <c r="L21" t="n">
-        <v>673.6</v>
+        <v>719.3</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>676</v>
+        <v>706</v>
       </c>
       <c r="C22" t="n">
-        <v>660</v>
+        <v>643</v>
       </c>
       <c r="D22" t="n">
-        <v>696</v>
+        <v>587</v>
       </c>
       <c r="E22" t="n">
-        <v>737</v>
+        <v>707</v>
       </c>
       <c r="F22" t="n">
-        <v>549</v>
+        <v>658</v>
       </c>
       <c r="G22" t="n">
-        <v>612</v>
+        <v>668</v>
       </c>
       <c r="H22" t="n">
-        <v>642</v>
+        <v>846</v>
       </c>
       <c r="I22" t="n">
-        <v>615</v>
+        <v>673</v>
       </c>
       <c r="J22" t="n">
-        <v>646</v>
+        <v>587</v>
       </c>
       <c r="K22" t="n">
-        <v>675</v>
+        <v>701</v>
       </c>
       <c r="L22" t="n">
-        <v>650.8</v>
+        <v>677.6</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>632</v>
+        <v>767</v>
       </c>
       <c r="C23" t="n">
-        <v>528</v>
+        <v>630</v>
       </c>
       <c r="D23" t="n">
-        <v>640</v>
+        <v>580</v>
       </c>
       <c r="E23" t="n">
-        <v>622</v>
+        <v>596</v>
       </c>
       <c r="F23" t="n">
-        <v>623</v>
+        <v>594</v>
       </c>
       <c r="G23" t="n">
-        <v>688</v>
+        <v>606</v>
       </c>
       <c r="H23" t="n">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="I23" t="n">
-        <v>704</v>
+        <v>595</v>
       </c>
       <c r="J23" t="n">
-        <v>560</v>
+        <v>626</v>
       </c>
       <c r="K23" t="n">
-        <v>628</v>
+        <v>562</v>
       </c>
       <c r="L23" t="n">
-        <v>625.5</v>
+        <v>619.4</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>728</v>
+        <v>695</v>
       </c>
       <c r="C24" t="n">
-        <v>651</v>
+        <v>662</v>
       </c>
       <c r="D24" t="n">
-        <v>727</v>
+        <v>894</v>
       </c>
       <c r="E24" t="n">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F24" t="n">
-        <v>695</v>
+        <v>716</v>
       </c>
       <c r="G24" t="n">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="H24" t="n">
-        <v>671</v>
+        <v>641</v>
       </c>
       <c r="I24" t="n">
-        <v>752</v>
+        <v>711</v>
       </c>
       <c r="J24" t="n">
-        <v>644</v>
+        <v>616</v>
       </c>
       <c r="K24" t="n">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="L24" t="n">
-        <v>705.1</v>
+        <v>710.3</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>566</v>
+        <v>744</v>
       </c>
       <c r="C25" t="n">
-        <v>710</v>
+        <v>649</v>
       </c>
       <c r="D25" t="n">
-        <v>554</v>
+        <v>698</v>
       </c>
       <c r="E25" t="n">
-        <v>560</v>
+        <v>731</v>
       </c>
       <c r="F25" t="n">
-        <v>627</v>
+        <v>646</v>
       </c>
       <c r="G25" t="n">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="H25" t="n">
-        <v>630</v>
+        <v>570</v>
       </c>
       <c r="I25" t="n">
-        <v>740</v>
+        <v>692</v>
       </c>
       <c r="J25" t="n">
-        <v>755</v>
+        <v>725</v>
       </c>
       <c r="K25" t="n">
-        <v>694</v>
+        <v>742</v>
       </c>
       <c r="L25" t="n">
-        <v>651.8</v>
+        <v>687.5</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>686</v>
+        <v>651</v>
       </c>
       <c r="C26" t="n">
-        <v>709</v>
+        <v>652</v>
       </c>
       <c r="D26" t="n">
-        <v>666</v>
+        <v>645</v>
       </c>
       <c r="E26" t="n">
-        <v>694</v>
+        <v>726</v>
       </c>
       <c r="F26" t="n">
-        <v>661</v>
+        <v>627</v>
       </c>
       <c r="G26" t="n">
-        <v>661</v>
+        <v>701</v>
       </c>
       <c r="H26" t="n">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="I26" t="n">
-        <v>790</v>
+        <v>712</v>
       </c>
       <c r="J26" t="n">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="K26" t="n">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="L26" t="n">
-        <v>693.3</v>
+        <v>677.2</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>571</v>
+        <v>581</v>
       </c>
       <c r="C27" t="n">
-        <v>581</v>
+        <v>703</v>
       </c>
       <c r="D27" t="n">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="E27" t="n">
-        <v>486</v>
+        <v>689</v>
       </c>
       <c r="F27" t="n">
-        <v>680</v>
+        <v>632</v>
       </c>
       <c r="G27" t="n">
-        <v>654</v>
+        <v>587</v>
       </c>
       <c r="H27" t="n">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="I27" t="n">
-        <v>691</v>
+        <v>677</v>
       </c>
       <c r="J27" t="n">
-        <v>637</v>
+        <v>566</v>
       </c>
       <c r="K27" t="n">
-        <v>612</v>
+        <v>521</v>
       </c>
       <c r="L27" t="n">
-        <v>607</v>
+        <v>612.5</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>650</v>
+        <v>712</v>
       </c>
       <c r="C28" t="n">
-        <v>632</v>
+        <v>721</v>
       </c>
       <c r="D28" t="n">
-        <v>688</v>
+        <v>656</v>
       </c>
       <c r="E28" t="n">
         <v>679</v>
       </c>
       <c r="F28" t="n">
-        <v>682</v>
+        <v>781</v>
       </c>
       <c r="G28" t="n">
-        <v>659</v>
+        <v>729</v>
       </c>
       <c r="H28" t="n">
-        <v>656</v>
+        <v>776</v>
       </c>
       <c r="I28" t="n">
-        <v>685</v>
+        <v>657</v>
       </c>
       <c r="J28" t="n">
-        <v>710</v>
+        <v>810</v>
       </c>
       <c r="K28" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="L28" t="n">
-        <v>673.3</v>
+        <v>722.2</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>736</v>
+        <v>629</v>
       </c>
       <c r="C29" t="n">
-        <v>744</v>
+        <v>716</v>
       </c>
       <c r="D29" t="n">
-        <v>620</v>
+        <v>745</v>
       </c>
       <c r="E29" t="n">
-        <v>642</v>
+        <v>606</v>
       </c>
       <c r="F29" t="n">
-        <v>771</v>
+        <v>695</v>
       </c>
       <c r="G29" t="n">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="H29" t="n">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="I29" t="n">
-        <v>670</v>
+        <v>779</v>
       </c>
       <c r="J29" t="n">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="K29" t="n">
-        <v>653</v>
+        <v>834</v>
       </c>
       <c r="L29" t="n">
-        <v>687.2</v>
+        <v>707.3</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>628</v>
+        <v>744</v>
       </c>
       <c r="C30" t="n">
-        <v>680</v>
+        <v>636</v>
       </c>
       <c r="D30" t="n">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="E30" t="n">
-        <v>651</v>
+        <v>746</v>
       </c>
       <c r="F30" t="n">
-        <v>699</v>
+        <v>640</v>
       </c>
       <c r="G30" t="n">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="H30" t="n">
-        <v>610</v>
+        <v>654</v>
       </c>
       <c r="I30" t="n">
-        <v>718</v>
+        <v>631</v>
       </c>
       <c r="J30" t="n">
-        <v>711</v>
+        <v>679</v>
       </c>
       <c r="K30" t="n">
-        <v>790</v>
+        <v>689</v>
       </c>
       <c r="L30" t="n">
-        <v>683.8</v>
+        <v>678.2</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="C31" t="n">
-        <v>756</v>
+        <v>788</v>
       </c>
       <c r="D31" t="n">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E31" t="n">
-        <v>736</v>
+        <v>784</v>
       </c>
       <c r="F31" t="n">
-        <v>813</v>
+        <v>639</v>
       </c>
       <c r="G31" t="n">
-        <v>702</v>
+        <v>804</v>
       </c>
       <c r="H31" t="n">
-        <v>741</v>
+        <v>678</v>
       </c>
       <c r="I31" t="n">
-        <v>698</v>
+        <v>683</v>
       </c>
       <c r="J31" t="n">
-        <v>657</v>
+        <v>639</v>
       </c>
       <c r="K31" t="n">
-        <v>706</v>
+        <v>655</v>
       </c>
       <c r="L31" t="n">
-        <v>737.6</v>
+        <v>723.3</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>704</v>
+        <v>730</v>
       </c>
       <c r="C32" t="n">
-        <v>676</v>
+        <v>722</v>
       </c>
       <c r="D32" t="n">
-        <v>713</v>
+        <v>761</v>
       </c>
       <c r="E32" t="n">
-        <v>744</v>
+        <v>665</v>
       </c>
       <c r="F32" t="n">
-        <v>690</v>
+        <v>750</v>
       </c>
       <c r="G32" t="n">
-        <v>706</v>
+        <v>821</v>
       </c>
       <c r="H32" t="n">
-        <v>674</v>
+        <v>731</v>
       </c>
       <c r="I32" t="n">
-        <v>713</v>
+        <v>760</v>
       </c>
       <c r="J32" t="n">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="K32" t="n">
-        <v>768</v>
+        <v>756</v>
       </c>
       <c r="L32" t="n">
-        <v>709.1</v>
+        <v>740.6</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>609</v>
+        <v>663</v>
       </c>
       <c r="C33" t="n">
-        <v>722</v>
+        <v>673</v>
       </c>
       <c r="D33" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E33" t="n">
-        <v>687</v>
+        <v>614</v>
       </c>
       <c r="F33" t="n">
-        <v>725</v>
+        <v>780</v>
       </c>
       <c r="G33" t="n">
-        <v>736</v>
+        <v>641</v>
       </c>
       <c r="H33" t="n">
-        <v>651</v>
+        <v>675</v>
       </c>
       <c r="I33" t="n">
-        <v>747</v>
+        <v>647</v>
       </c>
       <c r="J33" t="n">
-        <v>684</v>
+        <v>790</v>
       </c>
       <c r="K33" t="n">
-        <v>624</v>
+        <v>665</v>
       </c>
       <c r="L33" t="n">
-        <v>680.4</v>
+        <v>676.8</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>590</v>
+        <v>643</v>
       </c>
       <c r="C34" t="n">
-        <v>688</v>
+        <v>727</v>
       </c>
       <c r="D34" t="n">
-        <v>713</v>
+        <v>745</v>
       </c>
       <c r="E34" t="n">
-        <v>665</v>
+        <v>741</v>
       </c>
       <c r="F34" t="n">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="G34" t="n">
-        <v>638</v>
+        <v>703</v>
       </c>
       <c r="H34" t="n">
-        <v>714</v>
+        <v>655</v>
       </c>
       <c r="I34" t="n">
-        <v>766</v>
+        <v>815</v>
       </c>
       <c r="J34" t="n">
-        <v>611</v>
+        <v>663</v>
       </c>
       <c r="K34" t="n">
-        <v>700</v>
+        <v>751</v>
       </c>
       <c r="L34" t="n">
-        <v>674.5</v>
+        <v>711.5</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>612</v>
+        <v>641</v>
       </c>
       <c r="C35" t="n">
-        <v>688</v>
+        <v>659</v>
       </c>
       <c r="D35" t="n">
-        <v>658</v>
+        <v>644</v>
       </c>
       <c r="E35" t="n">
-        <v>674</v>
+        <v>592</v>
       </c>
       <c r="F35" t="n">
-        <v>644</v>
+        <v>752</v>
       </c>
       <c r="G35" t="n">
-        <v>738</v>
+        <v>618</v>
       </c>
       <c r="H35" t="n">
-        <v>644</v>
+        <v>558</v>
       </c>
       <c r="I35" t="n">
-        <v>716</v>
+        <v>588</v>
       </c>
       <c r="J35" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K35" t="n">
-        <v>644</v>
+        <v>614</v>
       </c>
       <c r="L35" t="n">
-        <v>664.2</v>
+        <v>629.1</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>742</v>
+        <v>638</v>
       </c>
       <c r="C36" t="n">
-        <v>785</v>
+        <v>650</v>
       </c>
       <c r="D36" t="n">
-        <v>780</v>
+        <v>617</v>
       </c>
       <c r="E36" t="n">
-        <v>692</v>
+        <v>758</v>
       </c>
       <c r="F36" t="n">
+        <v>762</v>
+      </c>
+      <c r="G36" t="n">
+        <v>725</v>
+      </c>
+      <c r="H36" t="n">
         <v>715</v>
       </c>
-      <c r="G36" t="n">
-        <v>671</v>
-      </c>
-      <c r="H36" t="n">
-        <v>651</v>
-      </c>
       <c r="I36" t="n">
-        <v>668</v>
+        <v>724</v>
       </c>
       <c r="J36" t="n">
-        <v>673</v>
+        <v>862</v>
       </c>
       <c r="K36" t="n">
-        <v>685</v>
+        <v>743</v>
       </c>
       <c r="L36" t="n">
-        <v>706.2</v>
+        <v>719.4</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>676</v>
+        <v>657</v>
       </c>
       <c r="C37" t="n">
-        <v>671</v>
+        <v>645</v>
       </c>
       <c r="D37" t="n">
-        <v>632</v>
+        <v>681</v>
       </c>
       <c r="E37" t="n">
-        <v>599</v>
+        <v>801</v>
       </c>
       <c r="F37" t="n">
-        <v>732</v>
+        <v>720</v>
       </c>
       <c r="G37" t="n">
-        <v>736</v>
+        <v>757</v>
       </c>
       <c r="H37" t="n">
-        <v>631</v>
+        <v>677</v>
       </c>
       <c r="I37" t="n">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="J37" t="n">
-        <v>741</v>
+        <v>581</v>
       </c>
       <c r="K37" t="n">
-        <v>648</v>
+        <v>664</v>
       </c>
       <c r="L37" t="n">
-        <v>673.7</v>
+        <v>684.9</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>697</v>
+        <v>662</v>
       </c>
       <c r="C38" t="n">
-        <v>626</v>
+        <v>604</v>
       </c>
       <c r="D38" t="n">
-        <v>582</v>
+        <v>676</v>
       </c>
       <c r="E38" t="n">
-        <v>686</v>
+        <v>723</v>
       </c>
       <c r="F38" t="n">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="G38" t="n">
-        <v>651</v>
+        <v>715</v>
       </c>
       <c r="H38" t="n">
-        <v>601</v>
+        <v>630</v>
       </c>
       <c r="I38" t="n">
+        <v>600</v>
+      </c>
+      <c r="J38" t="n">
         <v>593</v>
       </c>
-      <c r="J38" t="n">
-        <v>680</v>
-      </c>
       <c r="K38" t="n">
-        <v>631</v>
+        <v>656</v>
       </c>
       <c r="L38" t="n">
-        <v>632.4</v>
+        <v>643.8</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>550</v>
+        <v>520</v>
       </c>
       <c r="C39" t="n">
-        <v>542</v>
+        <v>595</v>
       </c>
       <c r="D39" t="n">
-        <v>516</v>
+        <v>688</v>
       </c>
       <c r="E39" t="n">
-        <v>538</v>
+        <v>589</v>
       </c>
       <c r="F39" t="n">
-        <v>578</v>
+        <v>632</v>
       </c>
       <c r="G39" t="n">
-        <v>675</v>
+        <v>564</v>
       </c>
       <c r="H39" t="n">
-        <v>582</v>
+        <v>647</v>
       </c>
       <c r="I39" t="n">
-        <v>663</v>
+        <v>643</v>
       </c>
       <c r="J39" t="n">
-        <v>571</v>
+        <v>621</v>
       </c>
       <c r="K39" t="n">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="L39" t="n">
-        <v>586.1</v>
+        <v>617</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>634</v>
+        <v>691</v>
       </c>
       <c r="C40" t="n">
-        <v>690</v>
+        <v>614</v>
       </c>
       <c r="D40" t="n">
-        <v>687</v>
+        <v>733</v>
       </c>
       <c r="E40" t="n">
-        <v>674</v>
+        <v>657</v>
       </c>
       <c r="F40" t="n">
-        <v>721</v>
+        <v>631</v>
       </c>
       <c r="G40" t="n">
-        <v>687</v>
+        <v>632</v>
       </c>
       <c r="H40" t="n">
-        <v>710</v>
+        <v>725</v>
       </c>
       <c r="I40" t="n">
-        <v>617</v>
+        <v>649</v>
       </c>
       <c r="J40" t="n">
-        <v>662</v>
+        <v>682</v>
       </c>
       <c r="K40" t="n">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="L40" t="n">
-        <v>677.5</v>
+        <v>671.1</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
+        <v>769</v>
+      </c>
+      <c r="C41" t="n">
+        <v>623</v>
+      </c>
+      <c r="D41" t="n">
+        <v>675</v>
+      </c>
+      <c r="E41" t="n">
+        <v>637</v>
+      </c>
+      <c r="F41" t="n">
+        <v>642</v>
+      </c>
+      <c r="G41" t="n">
+        <v>690</v>
+      </c>
+      <c r="H41" t="n">
+        <v>645</v>
+      </c>
+      <c r="I41" t="n">
+        <v>709</v>
+      </c>
+      <c r="J41" t="n">
         <v>662</v>
       </c>
-      <c r="C41" t="n">
-        <v>674</v>
-      </c>
-      <c r="D41" t="n">
-        <v>655</v>
-      </c>
-      <c r="E41" t="n">
-        <v>672</v>
-      </c>
-      <c r="F41" t="n">
-        <v>666</v>
-      </c>
-      <c r="G41" t="n">
-        <v>715</v>
-      </c>
-      <c r="H41" t="n">
-        <v>693</v>
-      </c>
-      <c r="I41" t="n">
-        <v>641</v>
-      </c>
-      <c r="J41" t="n">
-        <v>685</v>
-      </c>
       <c r="K41" t="n">
-        <v>758</v>
+        <v>724</v>
       </c>
       <c r="L41" t="n">
-        <v>682.1</v>
+        <v>677.6</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>721</v>
+        <v>817</v>
       </c>
       <c r="C42" t="n">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="D42" t="n">
-        <v>768</v>
+        <v>713</v>
       </c>
       <c r="E42" t="n">
-        <v>812</v>
+        <v>706</v>
       </c>
       <c r="F42" t="n">
-        <v>743</v>
+        <v>798</v>
       </c>
       <c r="G42" t="n">
-        <v>799</v>
+        <v>770</v>
       </c>
       <c r="H42" t="n">
-        <v>659</v>
+        <v>681</v>
       </c>
       <c r="I42" t="n">
-        <v>692</v>
+        <v>653</v>
       </c>
       <c r="J42" t="n">
-        <v>742</v>
+        <v>724</v>
       </c>
       <c r="K42" t="n">
-        <v>680</v>
+        <v>731</v>
       </c>
       <c r="L42" t="n">
-        <v>739.6</v>
+        <v>737.9</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>705</v>
+        <v>850</v>
       </c>
       <c r="C43" t="n">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="D43" t="n">
-        <v>744</v>
+        <v>683</v>
       </c>
       <c r="E43" t="n">
-        <v>663</v>
+        <v>723</v>
       </c>
       <c r="F43" t="n">
-        <v>659</v>
+        <v>704</v>
       </c>
       <c r="G43" t="n">
-        <v>689</v>
+        <v>668</v>
       </c>
       <c r="H43" t="n">
-        <v>714</v>
+        <v>690</v>
       </c>
       <c r="I43" t="n">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="J43" t="n">
-        <v>641</v>
+        <v>737</v>
       </c>
       <c r="K43" t="n">
-        <v>758</v>
+        <v>675</v>
       </c>
       <c r="L43" t="n">
-        <v>708.4</v>
+        <v>723.6</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="C44" t="n">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="D44" t="n">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="E44" t="n">
-        <v>598</v>
+        <v>628</v>
       </c>
       <c r="F44" t="n">
-        <v>549</v>
+        <v>738</v>
       </c>
       <c r="G44" t="n">
-        <v>758</v>
+        <v>724</v>
       </c>
       <c r="H44" t="n">
-        <v>667</v>
+        <v>653</v>
       </c>
       <c r="I44" t="n">
-        <v>693</v>
+        <v>634</v>
       </c>
       <c r="J44" t="n">
-        <v>590</v>
+        <v>725</v>
       </c>
       <c r="K44" t="n">
-        <v>673</v>
+        <v>580</v>
       </c>
       <c r="L44" t="n">
-        <v>656.5</v>
+        <v>673.4</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>619</v>
+        <v>703</v>
       </c>
       <c r="C45" t="n">
-        <v>760</v>
+        <v>622</v>
       </c>
       <c r="D45" t="n">
-        <v>730</v>
+        <v>770</v>
       </c>
       <c r="E45" t="n">
-        <v>684</v>
+        <v>750</v>
       </c>
       <c r="F45" t="n">
-        <v>749</v>
+        <v>698</v>
       </c>
       <c r="G45" t="n">
-        <v>782</v>
+        <v>650</v>
       </c>
       <c r="H45" t="n">
-        <v>811</v>
+        <v>732</v>
       </c>
       <c r="I45" t="n">
-        <v>726</v>
+        <v>783</v>
       </c>
       <c r="J45" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="K45" t="n">
-        <v>771</v>
+        <v>687</v>
       </c>
       <c r="L45" t="n">
-        <v>738.2</v>
+        <v>714.9</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>700</v>
+        <v>724</v>
       </c>
       <c r="C46" t="n">
-        <v>652</v>
+        <v>694</v>
       </c>
       <c r="D46" t="n">
-        <v>682</v>
+        <v>633</v>
       </c>
       <c r="E46" t="n">
-        <v>697</v>
+        <v>727</v>
       </c>
       <c r="F46" t="n">
-        <v>603</v>
+        <v>674</v>
       </c>
       <c r="G46" t="n">
-        <v>597</v>
+        <v>743</v>
       </c>
       <c r="H46" t="n">
-        <v>731</v>
+        <v>773</v>
       </c>
       <c r="I46" t="n">
-        <v>660</v>
+        <v>712</v>
       </c>
       <c r="J46" t="n">
-        <v>728</v>
+        <v>669</v>
       </c>
       <c r="K46" t="n">
-        <v>677</v>
+        <v>686</v>
       </c>
       <c r="L46" t="n">
-        <v>672.7</v>
+        <v>703.5</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>632</v>
+        <v>605</v>
       </c>
       <c r="C47" t="n">
-        <v>597</v>
+        <v>630</v>
       </c>
       <c r="D47" t="n">
-        <v>574</v>
+        <v>674</v>
       </c>
       <c r="E47" t="n">
-        <v>587</v>
+        <v>642</v>
       </c>
       <c r="F47" t="n">
-        <v>590</v>
+        <v>520</v>
       </c>
       <c r="G47" t="n">
-        <v>689</v>
+        <v>648</v>
       </c>
       <c r="H47" t="n">
-        <v>648</v>
+        <v>583</v>
       </c>
       <c r="I47" t="n">
         <v>577</v>
       </c>
       <c r="J47" t="n">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="K47" t="n">
-        <v>604</v>
+        <v>667</v>
       </c>
       <c r="L47" t="n">
-        <v>609.6</v>
+        <v>614.1</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>712</v>
+        <v>813</v>
       </c>
       <c r="C48" t="n">
-        <v>673</v>
+        <v>709</v>
       </c>
       <c r="D48" t="n">
-        <v>718</v>
+        <v>755</v>
       </c>
       <c r="E48" t="n">
-        <v>696</v>
+        <v>743</v>
       </c>
       <c r="F48" t="n">
-        <v>710</v>
+        <v>797</v>
       </c>
       <c r="G48" t="n">
-        <v>771</v>
+        <v>794</v>
       </c>
       <c r="H48" t="n">
-        <v>788</v>
+        <v>797</v>
       </c>
       <c r="I48" t="n">
-        <v>828</v>
+        <v>754</v>
       </c>
       <c r="J48" t="n">
-        <v>678</v>
+        <v>866</v>
       </c>
       <c r="K48" t="n">
-        <v>914</v>
+        <v>748</v>
       </c>
       <c r="L48" t="n">
-        <v>748.8</v>
+        <v>777.6</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>822</v>
+        <v>715</v>
       </c>
       <c r="C49" t="n">
+        <v>682</v>
+      </c>
+      <c r="D49" t="n">
+        <v>729</v>
+      </c>
+      <c r="E49" t="n">
+        <v>664</v>
+      </c>
+      <c r="F49" t="n">
+        <v>751</v>
+      </c>
+      <c r="G49" t="n">
+        <v>803</v>
+      </c>
+      <c r="H49" t="n">
+        <v>688</v>
+      </c>
+      <c r="I49" t="n">
         <v>693</v>
       </c>
-      <c r="D49" t="n">
-        <v>692</v>
-      </c>
-      <c r="E49" t="n">
-        <v>778</v>
-      </c>
-      <c r="F49" t="n">
-        <v>697</v>
-      </c>
-      <c r="G49" t="n">
-        <v>775</v>
-      </c>
-      <c r="H49" t="n">
-        <v>694</v>
-      </c>
-      <c r="I49" t="n">
-        <v>697</v>
-      </c>
       <c r="J49" t="n">
-        <v>723</v>
+        <v>623</v>
       </c>
       <c r="K49" t="n">
-        <v>736</v>
+        <v>770</v>
       </c>
       <c r="L49" t="n">
-        <v>730.7</v>
+        <v>711.8</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>752</v>
+        <v>813</v>
       </c>
       <c r="C50" t="n">
-        <v>709</v>
+        <v>666</v>
       </c>
       <c r="D50" t="n">
-        <v>699</v>
+        <v>606</v>
       </c>
       <c r="E50" t="n">
-        <v>697</v>
+        <v>737</v>
       </c>
       <c r="F50" t="n">
-        <v>723</v>
+        <v>673</v>
       </c>
       <c r="G50" t="n">
-        <v>630</v>
+        <v>662</v>
       </c>
       <c r="H50" t="n">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="I50" t="n">
-        <v>770</v>
+        <v>741</v>
       </c>
       <c r="J50" t="n">
-        <v>680</v>
+        <v>660</v>
       </c>
       <c r="K50" t="n">
-        <v>773</v>
+        <v>702</v>
       </c>
       <c r="L50" t="n">
-        <v>715.2</v>
+        <v>698.4</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>819</v>
+        <v>745</v>
       </c>
       <c r="C51" t="n">
-        <v>722</v>
+        <v>760</v>
       </c>
       <c r="D51" t="n">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="E51" t="n">
-        <v>612</v>
+        <v>677</v>
       </c>
       <c r="F51" t="n">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="G51" t="n">
-        <v>801</v>
+        <v>706</v>
       </c>
       <c r="H51" t="n">
-        <v>635</v>
+        <v>717</v>
       </c>
       <c r="I51" t="n">
-        <v>636</v>
+        <v>655</v>
       </c>
       <c r="J51" t="n">
-        <v>644</v>
+        <v>668</v>
       </c>
       <c r="K51" t="n">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="L51" t="n">
-        <v>704.5</v>
+        <v>710.2</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>675.96</v>
+        <v>688.38</v>
       </c>
       <c r="C52" t="n">
-        <v>669.84</v>
+        <v>684.6</v>
       </c>
       <c r="D52" t="n">
-        <v>669.5599999999999</v>
+        <v>682.9</v>
       </c>
       <c r="E52" t="n">
-        <v>664.72</v>
+        <v>678.72</v>
       </c>
       <c r="F52" t="n">
-        <v>669.3200000000001</v>
+        <v>690</v>
       </c>
       <c r="G52" t="n">
-        <v>682.52</v>
+        <v>674.92</v>
       </c>
       <c r="H52" t="n">
-        <v>672.46</v>
+        <v>680.08</v>
       </c>
       <c r="I52" t="n">
-        <v>682.92</v>
+        <v>688.1</v>
       </c>
       <c r="J52" t="n">
-        <v>670.8</v>
+        <v>668.3200000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>675.0599999999999</v>
+        <v>680.16</v>
       </c>
       <c r="L52" t="n">
-        <v>673.3159999999999</v>
+        <v>681.6180000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4.98263144493103</v>
+        <v>4.795941114425659</v>
       </c>
       <c r="C2" t="n">
-        <v>3.932724714279175</v>
+        <v>4.428705215454102</v>
       </c>
       <c r="D2" t="n">
-        <v>3.917249202728271</v>
+        <v>4.781840801239014</v>
       </c>
       <c r="E2" t="n">
-        <v>4.090338468551636</v>
+        <v>4.686537981033325</v>
       </c>
       <c r="F2" t="n">
-        <v>3.797183036804199</v>
+        <v>4.101044893264771</v>
       </c>
       <c r="G2" t="n">
-        <v>4.167025804519653</v>
+        <v>4.134960174560547</v>
       </c>
       <c r="H2" t="n">
-        <v>3.773626804351807</v>
+        <v>4.474585771560669</v>
       </c>
       <c r="I2" t="n">
-        <v>4.70916485786438</v>
+        <v>4.492047071456909</v>
       </c>
       <c r="J2" t="n">
-        <v>4.242153644561768</v>
+        <v>4.868079423904419</v>
       </c>
       <c r="K2" t="n">
-        <v>4.009612560272217</v>
+        <v>5.037168502807617</v>
       </c>
       <c r="L2" t="n">
-        <v>4.162171053886413</v>
+        <v>4.580091094970703</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>4.732223033905029</v>
+        <v>4.620208740234375</v>
       </c>
       <c r="C3" t="n">
-        <v>4.538097620010376</v>
+        <v>5.18983793258667</v>
       </c>
       <c r="D3" t="n">
-        <v>4.432235956192017</v>
+        <v>4.494050979614258</v>
       </c>
       <c r="E3" t="n">
-        <v>4.408171415328979</v>
+        <v>4.484068155288696</v>
       </c>
       <c r="F3" t="n">
-        <v>4.66361403465271</v>
+        <v>5.005247592926025</v>
       </c>
       <c r="G3" t="n">
-        <v>4.66975736618042</v>
+        <v>5.114446878433228</v>
       </c>
       <c r="H3" t="n">
-        <v>4.49089527130127</v>
+        <v>4.482559680938721</v>
       </c>
       <c r="I3" t="n">
-        <v>4.949633836746216</v>
+        <v>4.972351312637329</v>
       </c>
       <c r="J3" t="n">
-        <v>4.717077493667603</v>
+        <v>4.96935772895813</v>
       </c>
       <c r="K3" t="n">
-        <v>4.329502105712891</v>
+        <v>5.180331707000732</v>
       </c>
       <c r="L3" t="n">
-        <v>4.593120813369751</v>
+        <v>4.851246070861817</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>3.697166919708252</v>
+        <v>3.72650408744812</v>
       </c>
       <c r="C4" t="n">
-        <v>3.937588930130005</v>
+        <v>4.392879724502563</v>
       </c>
       <c r="D4" t="n">
-        <v>3.523665189743042</v>
+        <v>3.964401245117188</v>
       </c>
       <c r="E4" t="n">
-        <v>3.694450855255127</v>
+        <v>3.73695707321167</v>
       </c>
       <c r="F4" t="n">
-        <v>3.850053310394287</v>
+        <v>3.88261866569519</v>
       </c>
       <c r="G4" t="n">
-        <v>3.649778604507446</v>
+        <v>4.148933172225952</v>
       </c>
       <c r="H4" t="n">
-        <v>3.562351942062378</v>
+        <v>4.172361850738525</v>
       </c>
       <c r="I4" t="n">
-        <v>4.090506315231323</v>
+        <v>4.787800073623657</v>
       </c>
       <c r="J4" t="n">
-        <v>4.348995447158813</v>
+        <v>4.016750574111938</v>
       </c>
       <c r="K4" t="n">
-        <v>3.702518224716187</v>
+        <v>3.929508209228516</v>
       </c>
       <c r="L4" t="n">
-        <v>3.805707573890686</v>
+        <v>4.075871467590332</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>3.697238445281982</v>
+        <v>3.973139047622681</v>
       </c>
       <c r="C5" t="n">
-        <v>3.830158710479736</v>
+        <v>3.984632015228271</v>
       </c>
       <c r="D5" t="n">
-        <v>4.013190269470215</v>
+        <v>4.499809503555298</v>
       </c>
       <c r="E5" t="n">
-        <v>4.006342887878418</v>
+        <v>3.865920305252075</v>
       </c>
       <c r="F5" t="n">
-        <v>3.759052991867065</v>
+        <v>4.017050504684448</v>
       </c>
       <c r="G5" t="n">
-        <v>3.877241373062134</v>
+        <v>4.897233724594116</v>
       </c>
       <c r="H5" t="n">
-        <v>3.879653453826904</v>
+        <v>3.906338930130005</v>
       </c>
       <c r="I5" t="n">
-        <v>3.786443710327148</v>
+        <v>4.19208288192749</v>
       </c>
       <c r="J5" t="n">
-        <v>3.841405391693115</v>
+        <v>4.083896398544312</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8623046875</v>
+        <v>4.207041263580322</v>
       </c>
       <c r="L5" t="n">
-        <v>3.855303192138672</v>
+        <v>4.162714457511902</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>3.896445751190186</v>
+        <v>3.755227088928223</v>
       </c>
       <c r="C6" t="n">
-        <v>4.135920286178589</v>
+        <v>4.149692296981812</v>
       </c>
       <c r="D6" t="n">
-        <v>3.877535343170166</v>
+        <v>4.251932621002197</v>
       </c>
       <c r="E6" t="n">
-        <v>3.700709104537964</v>
+        <v>4.31225848197937</v>
       </c>
       <c r="F6" t="n">
-        <v>3.583881855010986</v>
+        <v>4.04797101020813</v>
       </c>
       <c r="G6" t="n">
-        <v>3.844141244888306</v>
+        <v>4.131747961044312</v>
       </c>
       <c r="H6" t="n">
-        <v>4.000015497207642</v>
+        <v>4.304287672042847</v>
       </c>
       <c r="I6" t="n">
-        <v>3.921490907669067</v>
+        <v>4.255478620529175</v>
       </c>
       <c r="J6" t="n">
-        <v>4.212283372879028</v>
+        <v>3.955157041549683</v>
       </c>
       <c r="K6" t="n">
-        <v>3.649813175201416</v>
+        <v>4.166155338287354</v>
       </c>
       <c r="L6" t="n">
-        <v>3.882223653793335</v>
+        <v>4.13299081325531</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>3.686055421829224</v>
+        <v>3.914300918579102</v>
       </c>
       <c r="C7" t="n">
-        <v>3.981634855270386</v>
+        <v>4.174643278121948</v>
       </c>
       <c r="D7" t="n">
-        <v>3.566381454467773</v>
+        <v>4.396562337875366</v>
       </c>
       <c r="E7" t="n">
-        <v>4.106683969497681</v>
+        <v>4.2130446434021</v>
       </c>
       <c r="F7" t="n">
-        <v>3.819127321243286</v>
+        <v>4.19209885597229</v>
       </c>
       <c r="G7" t="n">
-        <v>3.903995990753174</v>
+        <v>4.067910671234131</v>
       </c>
       <c r="H7" t="n">
-        <v>3.82234001159668</v>
+        <v>4.091855049133301</v>
       </c>
       <c r="I7" t="n">
-        <v>3.787972688674927</v>
+        <v>4.043477296829224</v>
       </c>
       <c r="J7" t="n">
-        <v>3.944280385971069</v>
+        <v>4.185107707977295</v>
       </c>
       <c r="K7" t="n">
-        <v>3.856275320053101</v>
+        <v>4.225992202758789</v>
       </c>
       <c r="L7" t="n">
-        <v>3.84747474193573</v>
+        <v>4.150499296188355</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>4.009193420410156</v>
+        <v>4.456428050994873</v>
       </c>
       <c r="C8" t="n">
-        <v>4.155763626098633</v>
+        <v>4.345717191696167</v>
       </c>
       <c r="D8" t="n">
-        <v>3.88373851776123</v>
+        <v>4.239989280700684</v>
       </c>
       <c r="E8" t="n">
-        <v>4.127288579940796</v>
+        <v>4.144702911376953</v>
       </c>
       <c r="F8" t="n">
-        <v>4.003988027572632</v>
+        <v>4.843982219696045</v>
       </c>
       <c r="G8" t="n">
-        <v>3.873743057250977</v>
+        <v>4.334237337112427</v>
       </c>
       <c r="H8" t="n">
-        <v>4.108678340911865</v>
+        <v>4.100815296173096</v>
       </c>
       <c r="I8" t="n">
-        <v>4.074274301528931</v>
+        <v>5.098899602890015</v>
       </c>
       <c r="J8" t="n">
-        <v>4.119130373001099</v>
+        <v>4.613003492355347</v>
       </c>
       <c r="K8" t="n">
-        <v>3.946168899536133</v>
+        <v>5.332648277282715</v>
       </c>
       <c r="L8" t="n">
-        <v>4.030196714401245</v>
+        <v>4.551042366027832</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>3.608874797821045</v>
+        <v>3.701866626739502</v>
       </c>
       <c r="C9" t="n">
-        <v>3.775125980377197</v>
+        <v>3.911315441131592</v>
       </c>
       <c r="D9" t="n">
-        <v>3.519354820251465</v>
+        <v>3.948704719543457</v>
       </c>
       <c r="E9" t="n">
-        <v>4.097023010253906</v>
+        <v>3.811093330383301</v>
       </c>
       <c r="F9" t="n">
-        <v>3.431079387664795</v>
+        <v>3.792618989944458</v>
       </c>
       <c r="G9" t="n">
-        <v>3.948329925537109</v>
+        <v>3.941757678985596</v>
       </c>
       <c r="H9" t="n">
-        <v>3.721564292907715</v>
+        <v>4.105835914611816</v>
       </c>
       <c r="I9" t="n">
-        <v>3.824536323547363</v>
+        <v>4.024534463882446</v>
       </c>
       <c r="J9" t="n">
-        <v>3.819567918777466</v>
+        <v>4.223013639450073</v>
       </c>
       <c r="K9" t="n">
-        <v>3.700093030929565</v>
+        <v>3.718806028366089</v>
       </c>
       <c r="L9" t="n">
-        <v>3.744554948806763</v>
+        <v>3.917954683303833</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>5.623617649078369</v>
+        <v>4.935144901275635</v>
       </c>
       <c r="C10" t="n">
-        <v>5.109732389450073</v>
+        <v>5.950007677078247</v>
       </c>
       <c r="D10" t="n">
-        <v>4.616508483886719</v>
+        <v>4.848369598388672</v>
       </c>
       <c r="E10" t="n">
-        <v>5.150888442993164</v>
+        <v>5.871207714080811</v>
       </c>
       <c r="F10" t="n">
-        <v>4.951786518096924</v>
+        <v>4.973044157028198</v>
       </c>
       <c r="G10" t="n">
-        <v>5.329908609390259</v>
+        <v>5.669239044189453</v>
       </c>
       <c r="H10" t="n">
-        <v>5.216464519500732</v>
+        <v>6.764413118362427</v>
       </c>
       <c r="I10" t="n">
-        <v>4.943580865859985</v>
+        <v>5.542087078094482</v>
       </c>
       <c r="J10" t="n">
-        <v>4.732682704925537</v>
+        <v>4.90074610710144</v>
       </c>
       <c r="K10" t="n">
-        <v>5.149248600006104</v>
+        <v>5.253320217132568</v>
       </c>
       <c r="L10" t="n">
-        <v>5.082441878318787</v>
+        <v>5.470757961273193</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>4.230177879333496</v>
+        <v>5.690305709838867</v>
       </c>
       <c r="C11" t="n">
-        <v>4.942823886871338</v>
+        <v>5.820948362350464</v>
       </c>
       <c r="D11" t="n">
-        <v>4.190399169921875</v>
+        <v>5.024426460266113</v>
       </c>
       <c r="E11" t="n">
-        <v>4.365602731704712</v>
+        <v>5.055827140808105</v>
       </c>
       <c r="F11" t="n">
-        <v>4.670005798339844</v>
+        <v>5.021956205368042</v>
       </c>
       <c r="G11" t="n">
-        <v>4.192595958709717</v>
+        <v>5.35107421875</v>
       </c>
       <c r="H11" t="n">
-        <v>4.450079441070557</v>
+        <v>5.358542442321777</v>
       </c>
       <c r="I11" t="n">
-        <v>4.384440422058105</v>
+        <v>5.113507747650146</v>
       </c>
       <c r="J11" t="n">
-        <v>4.333905220031738</v>
+        <v>4.765642881393433</v>
       </c>
       <c r="K11" t="n">
-        <v>4.25213623046875</v>
+        <v>4.469359874725342</v>
       </c>
       <c r="L11" t="n">
-        <v>4.401216673851013</v>
+        <v>5.167159104347229</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>3.929994344711304</v>
+        <v>4.199057817459106</v>
       </c>
       <c r="C12" t="n">
-        <v>4.115177869796753</v>
+        <v>3.928293466567993</v>
       </c>
       <c r="D12" t="n">
-        <v>4.200645685195923</v>
+        <v>4.19659686088562</v>
       </c>
       <c r="E12" t="n">
-        <v>3.904026508331299</v>
+        <v>4.101814985275269</v>
       </c>
       <c r="F12" t="n">
-        <v>3.959405899047852</v>
+        <v>4.185093879699707</v>
       </c>
       <c r="G12" t="n">
-        <v>4.243996620178223</v>
+        <v>4.14271354675293</v>
       </c>
       <c r="H12" t="n">
-        <v>3.832412958145142</v>
+        <v>4.33271861076355</v>
       </c>
       <c r="I12" t="n">
-        <v>4.154174566268921</v>
+        <v>4.151054620742798</v>
       </c>
       <c r="J12" t="n">
-        <v>4.157325744628906</v>
+        <v>4.400809526443481</v>
       </c>
       <c r="K12" t="n">
-        <v>3.986818313598633</v>
+        <v>3.980847120285034</v>
       </c>
       <c r="L12" t="n">
-        <v>4.048397850990296</v>
+        <v>4.161900043487549</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>4.297504425048828</v>
+        <v>5.31892466545105</v>
       </c>
       <c r="C13" t="n">
-        <v>4.364841938018799</v>
+        <v>5.834137916564941</v>
       </c>
       <c r="D13" t="n">
-        <v>4.522863864898682</v>
+        <v>6.282502174377441</v>
       </c>
       <c r="E13" t="n">
-        <v>5.379477262496948</v>
+        <v>5.185259819030762</v>
       </c>
       <c r="F13" t="n">
-        <v>4.661126613616943</v>
+        <v>5.418692588806152</v>
       </c>
       <c r="G13" t="n">
-        <v>5.529304504394531</v>
+        <v>5.588266134262085</v>
       </c>
       <c r="H13" t="n">
-        <v>4.090669393539429</v>
+        <v>5.79227876663208</v>
       </c>
       <c r="I13" t="n">
-        <v>4.64258074760437</v>
+        <v>5.609695196151733</v>
       </c>
       <c r="J13" t="n">
-        <v>4.357966899871826</v>
+        <v>4.991280317306519</v>
       </c>
       <c r="K13" t="n">
-        <v>4.696408748626709</v>
+        <v>5.267553091049194</v>
       </c>
       <c r="L13" t="n">
-        <v>4.654274439811706</v>
+        <v>5.528859066963196</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>4.587834596633911</v>
+        <v>4.761861324310303</v>
       </c>
       <c r="C14" t="n">
-        <v>4.211230039596558</v>
+        <v>4.319475173950195</v>
       </c>
       <c r="D14" t="n">
-        <v>4.625576496124268</v>
+        <v>4.765847444534302</v>
       </c>
       <c r="E14" t="n">
-        <v>4.176844358444214</v>
+        <v>4.374369859695435</v>
       </c>
       <c r="F14" t="n">
-        <v>4.426415681838989</v>
+        <v>4.871098518371582</v>
       </c>
       <c r="G14" t="n">
-        <v>4.065799236297607</v>
+        <v>4.199285268783569</v>
       </c>
       <c r="H14" t="n">
-        <v>4.917261600494385</v>
+        <v>4.599297761917114</v>
       </c>
       <c r="I14" t="n">
-        <v>4.358834743499756</v>
+        <v>4.827678680419922</v>
       </c>
       <c r="J14" t="n">
-        <v>4.062364339828491</v>
+        <v>4.267122030258179</v>
       </c>
       <c r="K14" t="n">
-        <v>4.714767932891846</v>
+        <v>4.455133676528931</v>
       </c>
       <c r="L14" t="n">
-        <v>4.414692902565003</v>
+        <v>4.544116973876953</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>4.819706439971924</v>
+        <v>4.970799684524536</v>
       </c>
       <c r="C15" t="n">
-        <v>4.826524019241333</v>
+        <v>5.218694686889648</v>
       </c>
       <c r="D15" t="n">
-        <v>4.969772815704346</v>
+        <v>5.044746398925781</v>
       </c>
       <c r="E15" t="n">
-        <v>4.932851552963257</v>
+        <v>5.053086996078491</v>
       </c>
       <c r="F15" t="n">
-        <v>4.439658641815186</v>
+        <v>4.528946876525879</v>
       </c>
       <c r="G15" t="n">
-        <v>4.580175638198853</v>
+        <v>4.895018577575684</v>
       </c>
       <c r="H15" t="n">
-        <v>4.730026006698608</v>
+        <v>5.197775840759277</v>
       </c>
       <c r="I15" t="n">
-        <v>5.210593461990356</v>
+        <v>4.906977415084839</v>
       </c>
       <c r="J15" t="n">
-        <v>4.71881628036499</v>
+        <v>5.406236886978149</v>
       </c>
       <c r="K15" t="n">
-        <v>4.627723693847656</v>
+        <v>5.159340143203735</v>
       </c>
       <c r="L15" t="n">
-        <v>4.785584855079651</v>
+        <v>5.038162350654602</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>4.303114414215088</v>
+        <v>5.419176578521729</v>
       </c>
       <c r="C16" t="n">
-        <v>4.126433849334717</v>
+        <v>4.422744035720825</v>
       </c>
       <c r="D16" t="n">
-        <v>4.119202375411987</v>
+        <v>4.330453872680664</v>
       </c>
       <c r="E16" t="n">
-        <v>4.090450763702393</v>
+        <v>4.671604871749878</v>
       </c>
       <c r="F16" t="n">
-        <v>4.372418165206909</v>
+        <v>4.132961750030518</v>
       </c>
       <c r="G16" t="n">
-        <v>4.480793237686157</v>
+        <v>4.380817890167236</v>
       </c>
       <c r="H16" t="n">
-        <v>4.16612696647644</v>
+        <v>4.165887594223022</v>
       </c>
       <c r="I16" t="n">
-        <v>4.226855039596558</v>
+        <v>4.127585887908936</v>
       </c>
       <c r="J16" t="n">
-        <v>4.594980001449585</v>
+        <v>4.093063354492188</v>
       </c>
       <c r="K16" t="n">
-        <v>4.291650295257568</v>
+        <v>4.342977285385132</v>
       </c>
       <c r="L16" t="n">
-        <v>4.277202510833741</v>
+        <v>4.408727312088013</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>4.919042825698853</v>
+        <v>4.390830278396606</v>
       </c>
       <c r="C17" t="n">
-        <v>4.153332233428955</v>
+        <v>4.785275936126709</v>
       </c>
       <c r="D17" t="n">
-        <v>4.805145740509033</v>
+        <v>4.984302997589111</v>
       </c>
       <c r="E17" t="n">
-        <v>4.874678134918213</v>
+        <v>4.419727563858032</v>
       </c>
       <c r="F17" t="n">
-        <v>4.383443593978882</v>
+        <v>5.783012866973877</v>
       </c>
       <c r="G17" t="n">
-        <v>4.102028608322144</v>
+        <v>5.132411479949951</v>
       </c>
       <c r="H17" t="n">
-        <v>4.318906784057617</v>
+        <v>4.274111032485962</v>
       </c>
       <c r="I17" t="n">
-        <v>4.552578687667847</v>
+        <v>4.495049715042114</v>
       </c>
       <c r="J17" t="n">
-        <v>4.887230157852173</v>
+        <v>4.723464727401733</v>
       </c>
       <c r="K17" t="n">
-        <v>4.352579593658447</v>
+        <v>4.680568933486938</v>
       </c>
       <c r="L17" t="n">
-        <v>4.534896636009217</v>
+        <v>4.766875553131103</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>4.272378206253052</v>
+        <v>4.97131085395813</v>
       </c>
       <c r="C18" t="n">
-        <v>4.270918607711792</v>
+        <v>4.160904884338379</v>
       </c>
       <c r="D18" t="n">
-        <v>4.233978271484375</v>
+        <v>4.732962608337402</v>
       </c>
       <c r="E18" t="n">
-        <v>4.537126064300537</v>
+        <v>4.419724225997925</v>
       </c>
       <c r="F18" t="n">
-        <v>4.238758563995361</v>
+        <v>4.890526056289673</v>
       </c>
       <c r="G18" t="n">
-        <v>4.113684415817261</v>
+        <v>5.110471963882446</v>
       </c>
       <c r="H18" t="n">
-        <v>4.313004970550537</v>
+        <v>5.095532655715942</v>
       </c>
       <c r="I18" t="n">
-        <v>3.937832593917847</v>
+        <v>4.639704465866089</v>
       </c>
       <c r="J18" t="n">
-        <v>4.161033153533936</v>
+        <v>5.169307947158813</v>
       </c>
       <c r="K18" t="n">
-        <v>4.256672143936157</v>
+        <v>4.725448369979858</v>
       </c>
       <c r="L18" t="n">
-        <v>4.233538699150086</v>
+        <v>4.791589403152466</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>3.85027003288269</v>
+        <v>4.60332727432251</v>
       </c>
       <c r="C19" t="n">
-        <v>4.483517169952393</v>
+        <v>4.547458171844482</v>
       </c>
       <c r="D19" t="n">
-        <v>4.621302127838135</v>
+        <v>4.335463762283325</v>
       </c>
       <c r="E19" t="n">
-        <v>4.392104387283325</v>
+        <v>4.004788398742676</v>
       </c>
       <c r="F19" t="n">
-        <v>4.049160480499268</v>
+        <v>4.469144582748413</v>
       </c>
       <c r="G19" t="n">
-        <v>3.95635986328125</v>
+        <v>4.104047536849976</v>
       </c>
       <c r="H19" t="n">
-        <v>4.183400392532349</v>
+        <v>4.34746265411377</v>
       </c>
       <c r="I19" t="n">
-        <v>3.968668460845947</v>
+        <v>4.239984273910522</v>
       </c>
       <c r="J19" t="n">
-        <v>4.07002329826355</v>
+        <v>4.314256429672241</v>
       </c>
       <c r="K19" t="n">
-        <v>3.90140175819397</v>
+        <v>4.67134952545166</v>
       </c>
       <c r="L19" t="n">
-        <v>4.147620797157288</v>
+        <v>4.363728260993957</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>5.556883811950684</v>
+        <v>5.876186847686768</v>
       </c>
       <c r="C20" t="n">
-        <v>4.264748096466064</v>
+        <v>5.287239074707031</v>
       </c>
       <c r="D20" t="n">
-        <v>5.166295766830444</v>
+        <v>5.532583951950073</v>
       </c>
       <c r="E20" t="n">
-        <v>5.383514404296875</v>
+        <v>4.949625253677368</v>
       </c>
       <c r="F20" t="n">
-        <v>5.136385202407837</v>
+        <v>4.894759893417358</v>
       </c>
       <c r="G20" t="n">
-        <v>4.934600591659546</v>
+        <v>4.842393636703491</v>
       </c>
       <c r="H20" t="n">
-        <v>5.107667446136475</v>
+        <v>5.356066942214966</v>
       </c>
       <c r="I20" t="n">
-        <v>4.841513156890869</v>
+        <v>5.291240930557251</v>
       </c>
       <c r="J20" t="n">
-        <v>4.558227777481079</v>
+        <v>5.083261966705322</v>
       </c>
       <c r="K20" t="n">
-        <v>4.694064617156982</v>
+        <v>5.546571969985962</v>
       </c>
       <c r="L20" t="n">
-        <v>4.964390087127685</v>
+        <v>5.265993046760559</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>4.549680948257446</v>
+        <v>4.351162433624268</v>
       </c>
       <c r="C21" t="n">
-        <v>4.25956392288208</v>
+        <v>5.221419811248779</v>
       </c>
       <c r="D21" t="n">
-        <v>3.923669576644897</v>
+        <v>4.769579410552979</v>
       </c>
       <c r="E21" t="n">
-        <v>4.862258434295654</v>
+        <v>4.303292512893677</v>
       </c>
       <c r="F21" t="n">
-        <v>4.564049243927002</v>
+        <v>4.690298080444336</v>
       </c>
       <c r="G21" t="n">
-        <v>4.311530351638794</v>
+        <v>4.647906303405762</v>
       </c>
       <c r="H21" t="n">
-        <v>3.932639360427856</v>
+        <v>5.130179882049561</v>
       </c>
       <c r="I21" t="n">
-        <v>4.846303462982178</v>
+        <v>5.143100738525391</v>
       </c>
       <c r="J21" t="n">
-        <v>4.400023460388184</v>
+        <v>4.619963407516479</v>
       </c>
       <c r="K21" t="n">
-        <v>4.289447069168091</v>
+        <v>4.344206094741821</v>
       </c>
       <c r="L21" t="n">
-        <v>4.393916583061218</v>
+        <v>4.722110867500305</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>4.47266960144043</v>
+        <v>5.232370376586914</v>
       </c>
       <c r="C22" t="n">
-        <v>4.930851697921753</v>
+        <v>5.010966777801514</v>
       </c>
       <c r="D22" t="n">
-        <v>4.556030988693237</v>
+        <v>4.745000600814819</v>
       </c>
       <c r="E22" t="n">
-        <v>4.734926223754883</v>
+        <v>4.991278409957886</v>
       </c>
       <c r="F22" t="n">
-        <v>4.435546159744263</v>
+        <v>4.610249280929565</v>
       </c>
       <c r="G22" t="n">
-        <v>4.279850721359253</v>
+        <v>4.416734218597412</v>
       </c>
       <c r="H22" t="n">
-        <v>4.450145721435547</v>
+        <v>5.135403871536255</v>
       </c>
       <c r="I22" t="n">
-        <v>4.481302261352539</v>
+        <v>4.80674409866333</v>
       </c>
       <c r="J22" t="n">
-        <v>4.496704339981079</v>
+        <v>4.578823804855347</v>
       </c>
       <c r="K22" t="n">
-        <v>4.220941543579102</v>
+        <v>5.359332323074341</v>
       </c>
       <c r="L22" t="n">
-        <v>4.505896925926208</v>
+        <v>4.888690376281739</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>4.048961639404297</v>
+        <v>5.279060840606689</v>
       </c>
       <c r="C23" t="n">
-        <v>3.873724460601807</v>
+        <v>4.457674264907837</v>
       </c>
       <c r="D23" t="n">
-        <v>4.432943820953369</v>
+        <v>4.265717029571533</v>
       </c>
       <c r="E23" t="n">
-        <v>3.945508718490601</v>
+        <v>4.146902322769165</v>
       </c>
       <c r="F23" t="n">
-        <v>3.922577857971191</v>
+        <v>4.362871646881104</v>
       </c>
       <c r="G23" t="n">
-        <v>4.149503231048584</v>
+        <v>4.25715184211731</v>
       </c>
       <c r="H23" t="n">
-        <v>3.96379828453064</v>
+        <v>4.339428663253784</v>
       </c>
       <c r="I23" t="n">
-        <v>4.360151290893555</v>
+        <v>4.363865613937378</v>
       </c>
       <c r="J23" t="n">
-        <v>3.937643766403198</v>
+        <v>4.104019641876221</v>
       </c>
       <c r="K23" t="n">
-        <v>4.042119026184082</v>
+        <v>4.146918296813965</v>
       </c>
       <c r="L23" t="n">
-        <v>4.067693209648132</v>
+        <v>4.372361016273499</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>5.231128931045532</v>
+        <v>4.726955890655518</v>
       </c>
       <c r="C24" t="n">
-        <v>4.454185009002686</v>
+        <v>4.865595579147339</v>
       </c>
       <c r="D24" t="n">
-        <v>4.557241439819336</v>
+        <v>5.120455503463745</v>
       </c>
       <c r="E24" t="n">
-        <v>4.875391006469727</v>
+        <v>5.223690032958984</v>
       </c>
       <c r="F24" t="n">
-        <v>4.532891035079956</v>
+        <v>4.773849487304688</v>
       </c>
       <c r="G24" t="n">
-        <v>4.932795763015747</v>
+        <v>4.89806056022644</v>
       </c>
       <c r="H24" t="n">
-        <v>4.335262537002563</v>
+        <v>4.536930084228516</v>
       </c>
       <c r="I24" t="n">
-        <v>4.848780393600464</v>
+        <v>4.715471029281616</v>
       </c>
       <c r="J24" t="n">
-        <v>4.435385942459106</v>
+        <v>4.746406316757202</v>
       </c>
       <c r="K24" t="n">
-        <v>4.743890762329102</v>
+        <v>5.136404752731323</v>
       </c>
       <c r="L24" t="n">
-        <v>4.694695281982422</v>
+        <v>4.874381923675537</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>4.858197689056396</v>
+        <v>5.592739820480347</v>
       </c>
       <c r="C25" t="n">
-        <v>4.424429178237915</v>
+        <v>4.656163454055786</v>
       </c>
       <c r="D25" t="n">
-        <v>3.92556619644165</v>
+        <v>4.98530101776123</v>
       </c>
       <c r="E25" t="n">
-        <v>3.99293851852417</v>
+        <v>5.329240560531616</v>
       </c>
       <c r="F25" t="n">
-        <v>4.298031091690063</v>
+        <v>4.446436643600464</v>
       </c>
       <c r="G25" t="n">
-        <v>5.096304893493652</v>
+        <v>4.633931398391724</v>
       </c>
       <c r="H25" t="n">
-        <v>4.065169811248779</v>
+        <v>4.457421064376831</v>
       </c>
       <c r="I25" t="n">
-        <v>5.073856830596924</v>
+        <v>4.942141056060791</v>
       </c>
       <c r="J25" t="n">
-        <v>5.254451751708984</v>
+        <v>5.622426271438599</v>
       </c>
       <c r="K25" t="n">
-        <v>4.669256687164307</v>
+        <v>5.642305850982666</v>
       </c>
       <c r="L25" t="n">
-        <v>4.565820264816284</v>
+        <v>5.030810713768005</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>4.227934837341309</v>
+        <v>5.116173267364502</v>
       </c>
       <c r="C26" t="n">
-        <v>4.121002197265625</v>
+        <v>5.197467088699341</v>
       </c>
       <c r="D26" t="n">
-        <v>4.621163368225098</v>
+        <v>4.575093507766724</v>
       </c>
       <c r="E26" t="n">
-        <v>3.856684923171997</v>
+        <v>4.095828771591187</v>
       </c>
       <c r="F26" t="n">
-        <v>4.959282159805298</v>
+        <v>5.118212699890137</v>
       </c>
       <c r="G26" t="n">
-        <v>4.569727182388306</v>
+        <v>5.303693532943726</v>
       </c>
       <c r="H26" t="n">
-        <v>4.470278024673462</v>
+        <v>4.782048940658569</v>
       </c>
       <c r="I26" t="n">
-        <v>5.281329154968262</v>
+        <v>4.651393413543701</v>
       </c>
       <c r="J26" t="n">
-        <v>4.431293725967407</v>
+        <v>4.61696982383728</v>
       </c>
       <c r="K26" t="n">
-        <v>4.717147350311279</v>
+        <v>5.488224744796753</v>
       </c>
       <c r="L26" t="n">
-        <v>4.525584292411804</v>
+        <v>4.894510579109192</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>3.74760890007019</v>
+        <v>4.26087760925293</v>
       </c>
       <c r="C27" t="n">
-        <v>3.705855369567871</v>
+        <v>4.486848592758179</v>
       </c>
       <c r="D27" t="n">
-        <v>4.076029539108276</v>
+        <v>3.796148538589478</v>
       </c>
       <c r="E27" t="n">
-        <v>3.811463117599487</v>
+        <v>4.656896829605103</v>
       </c>
       <c r="F27" t="n">
-        <v>4.244524955749512</v>
+        <v>4.132231950759888</v>
       </c>
       <c r="G27" t="n">
-        <v>5.477704286575317</v>
+        <v>4.040510416030884</v>
       </c>
       <c r="H27" t="n">
-        <v>3.874883413314819</v>
+        <v>4.139993906021118</v>
       </c>
       <c r="I27" t="n">
-        <v>4.315959215164185</v>
+        <v>4.489049673080444</v>
       </c>
       <c r="J27" t="n">
-        <v>4.059528350830078</v>
+        <v>4.2905592918396</v>
       </c>
       <c r="K27" t="n">
-        <v>4.13908576965332</v>
+        <v>3.936462640762329</v>
       </c>
       <c r="L27" t="n">
-        <v>4.145264291763306</v>
+        <v>4.222957944869995</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>4.461836814880371</v>
+        <v>4.316489458084106</v>
       </c>
       <c r="C28" t="n">
-        <v>3.799565076828003</v>
+        <v>4.996260404586792</v>
       </c>
       <c r="D28" t="n">
-        <v>3.917794704437256</v>
+        <v>4.29257345199585</v>
       </c>
       <c r="E28" t="n">
-        <v>4.34087872505188</v>
+        <v>4.677603244781494</v>
       </c>
       <c r="F28" t="n">
-        <v>3.978718519210815</v>
+        <v>5.122439622879028</v>
       </c>
       <c r="G28" t="n">
-        <v>4.414369583129883</v>
+        <v>4.373340368270874</v>
       </c>
       <c r="H28" t="n">
-        <v>4.007890701293945</v>
+        <v>4.782868385314941</v>
       </c>
       <c r="I28" t="n">
-        <v>4.34607982635498</v>
+        <v>4.651658773422241</v>
       </c>
       <c r="J28" t="n">
-        <v>4.105542898178101</v>
+        <v>4.946869134902954</v>
       </c>
       <c r="K28" t="n">
-        <v>4.154863595962524</v>
+        <v>4.952893018722534</v>
       </c>
       <c r="L28" t="n">
-        <v>4.152754044532776</v>
+        <v>4.711299586296081</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>4.900140285491943</v>
+        <v>4.407751083374023</v>
       </c>
       <c r="C29" t="n">
-        <v>4.462240219116211</v>
+        <v>4.153414249420166</v>
       </c>
       <c r="D29" t="n">
-        <v>4.044623374938965</v>
+        <v>4.966835737228394</v>
       </c>
       <c r="E29" t="n">
-        <v>4.614486217498779</v>
+        <v>4.319980621337891</v>
       </c>
       <c r="F29" t="n">
-        <v>4.753681898117065</v>
+        <v>4.685062408447266</v>
       </c>
       <c r="G29" t="n">
-        <v>4.109289169311523</v>
+        <v>4.702496528625488</v>
       </c>
       <c r="H29" t="n">
-        <v>4.257217645645142</v>
+        <v>4.599281311035156</v>
       </c>
       <c r="I29" t="n">
-        <v>4.068158626556396</v>
+        <v>5.276050806045532</v>
       </c>
       <c r="J29" t="n">
-        <v>4.020643711090088</v>
+        <v>4.464627027511597</v>
       </c>
       <c r="K29" t="n">
-        <v>4.275161743164062</v>
+        <v>5.425157785415649</v>
       </c>
       <c r="L29" t="n">
-        <v>4.350564289093017</v>
+        <v>4.700065755844117</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>4.286035776138306</v>
+        <v>5.404293537139893</v>
       </c>
       <c r="C30" t="n">
-        <v>4.118184804916382</v>
+        <v>4.4925537109375</v>
       </c>
       <c r="D30" t="n">
-        <v>4.111607313156128</v>
+        <v>4.641712427139282</v>
       </c>
       <c r="E30" t="n">
-        <v>4.214136600494385</v>
+        <v>5.387945413589478</v>
       </c>
       <c r="F30" t="n">
-        <v>4.370890378952026</v>
+        <v>4.55221700668335</v>
       </c>
       <c r="G30" t="n">
-        <v>4.408148765563965</v>
+        <v>4.800524234771729</v>
       </c>
       <c r="H30" t="n">
-        <v>3.66152548789978</v>
+        <v>4.547681331634521</v>
       </c>
       <c r="I30" t="n">
-        <v>4.379227638244629</v>
+        <v>4.710280418395996</v>
       </c>
       <c r="J30" t="n">
-        <v>4.246361494064331</v>
+        <v>4.647454977035522</v>
       </c>
       <c r="K30" t="n">
-        <v>4.698410749435425</v>
+        <v>4.708261728286743</v>
       </c>
       <c r="L30" t="n">
-        <v>4.249452900886536</v>
+        <v>4.789292478561402</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>4.55695652961731</v>
+        <v>4.802526712417603</v>
       </c>
       <c r="C31" t="n">
-        <v>4.141036748886108</v>
+        <v>5.098736524581909</v>
       </c>
       <c r="D31" t="n">
-        <v>5.118962049484253</v>
+        <v>5.503157615661621</v>
       </c>
       <c r="E31" t="n">
-        <v>4.335386514663696</v>
+        <v>4.85983943939209</v>
       </c>
       <c r="F31" t="n">
-        <v>4.854728221893311</v>
+        <v>4.538668394088745</v>
       </c>
       <c r="G31" t="n">
-        <v>4.247395515441895</v>
+        <v>4.982033252716064</v>
       </c>
       <c r="H31" t="n">
-        <v>4.61818528175354</v>
+        <v>4.948612213134766</v>
       </c>
       <c r="I31" t="n">
-        <v>4.100390911102295</v>
+        <v>4.608000040054321</v>
       </c>
       <c r="J31" t="n">
-        <v>4.630289077758789</v>
+        <v>4.60600733757019</v>
       </c>
       <c r="K31" t="n">
-        <v>4.596168279647827</v>
+        <v>4.671326398849487</v>
       </c>
       <c r="L31" t="n">
-        <v>4.519949913024902</v>
+        <v>4.86189079284668</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>4.421644687652588</v>
+        <v>4.971101522445679</v>
       </c>
       <c r="C32" t="n">
-        <v>4.433058261871338</v>
+        <v>4.92099666595459</v>
       </c>
       <c r="D32" t="n">
-        <v>4.338764429092407</v>
+        <v>4.951611042022705</v>
       </c>
       <c r="E32" t="n">
-        <v>4.920410394668579</v>
+        <v>4.970053672790527</v>
       </c>
       <c r="F32" t="n">
-        <v>4.91265869140625</v>
+        <v>4.970555543899536</v>
       </c>
       <c r="G32" t="n">
-        <v>4.821012735366821</v>
+        <v>5.122220993041992</v>
       </c>
       <c r="H32" t="n">
-        <v>4.537258386611938</v>
+        <v>4.681322813034058</v>
       </c>
       <c r="I32" t="n">
-        <v>4.654172897338867</v>
+        <v>5.376989126205444</v>
       </c>
       <c r="J32" t="n">
-        <v>5.058813095092773</v>
+        <v>4.642891645431519</v>
       </c>
       <c r="K32" t="n">
-        <v>5.22792911529541</v>
+        <v>4.933780908584595</v>
       </c>
       <c r="L32" t="n">
-        <v>4.732572269439697</v>
+        <v>4.954152393341064</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>4.022479295730591</v>
+        <v>4.388819217681885</v>
       </c>
       <c r="C33" t="n">
-        <v>4.294887065887451</v>
+        <v>4.469152927398682</v>
       </c>
       <c r="D33" t="n">
-        <v>4.14836311340332</v>
+        <v>4.544914722442627</v>
       </c>
       <c r="E33" t="n">
-        <v>4.235961437225342</v>
+        <v>4.737437725067139</v>
       </c>
       <c r="F33" t="n">
-        <v>4.203816890716553</v>
+        <v>4.652145862579346</v>
       </c>
       <c r="G33" t="n">
-        <v>4.859962224960327</v>
+        <v>4.369858980178833</v>
       </c>
       <c r="H33" t="n">
-        <v>4.672527313232422</v>
+        <v>4.575836658477783</v>
       </c>
       <c r="I33" t="n">
-        <v>4.363670110702515</v>
+        <v>4.257653713226318</v>
       </c>
       <c r="J33" t="n">
-        <v>4.094922304153442</v>
+        <v>4.586811065673828</v>
       </c>
       <c r="K33" t="n">
-        <v>3.963433027267456</v>
+        <v>4.503009080886841</v>
       </c>
       <c r="L33" t="n">
-        <v>4.286002278327942</v>
+        <v>4.508563995361328</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>3.656729221343994</v>
+        <v>3.958416223526001</v>
       </c>
       <c r="C34" t="n">
-        <v>4.786817789077759</v>
+        <v>4.717467308044434</v>
       </c>
       <c r="D34" t="n">
-        <v>4.52411413192749</v>
+        <v>4.454141855239868</v>
       </c>
       <c r="E34" t="n">
-        <v>3.681401014328003</v>
+        <v>4.461766004562378</v>
       </c>
       <c r="F34" t="n">
-        <v>3.573235750198364</v>
+        <v>4.460904359817505</v>
       </c>
       <c r="G34" t="n">
-        <v>3.571674346923828</v>
+        <v>4.353195428848267</v>
       </c>
       <c r="H34" t="n">
-        <v>3.788343667984009</v>
+        <v>4.452927589416504</v>
       </c>
       <c r="I34" t="n">
-        <v>4.668513536453247</v>
+        <v>4.520737409591675</v>
       </c>
       <c r="J34" t="n">
-        <v>3.761535406112671</v>
+        <v>4.372119426727295</v>
       </c>
       <c r="K34" t="n">
-        <v>3.89062762260437</v>
+        <v>4.724194288253784</v>
       </c>
       <c r="L34" t="n">
-        <v>3.990299248695373</v>
+        <v>4.447586989402771</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>3.76486611366272</v>
+        <v>4.161651611328125</v>
       </c>
       <c r="C35" t="n">
-        <v>4.467427492141724</v>
+        <v>4.09683084487915</v>
       </c>
       <c r="D35" t="n">
-        <v>4.289836406707764</v>
+        <v>4.423483610153198</v>
       </c>
       <c r="E35" t="n">
-        <v>4.081005334854126</v>
+        <v>3.857967853546143</v>
       </c>
       <c r="F35" t="n">
-        <v>3.786165237426758</v>
+        <v>4.465604543685913</v>
       </c>
       <c r="G35" t="n">
-        <v>5.106448411941528</v>
+        <v>4.264623641967773</v>
       </c>
       <c r="H35" t="n">
-        <v>3.856731653213501</v>
+        <v>4.747443675994873</v>
       </c>
       <c r="I35" t="n">
-        <v>3.640624761581421</v>
+        <v>8.927116632461548</v>
       </c>
       <c r="J35" t="n">
-        <v>3.981686592102051</v>
+        <v>3.92749285697937</v>
       </c>
       <c r="K35" t="n">
-        <v>3.764392614364624</v>
+        <v>4.1354820728302</v>
       </c>
       <c r="L35" t="n">
-        <v>4.073918461799622</v>
+        <v>4.70076973438263</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>4.06699800491333</v>
+        <v>4.15190577507019</v>
       </c>
       <c r="C36" t="n">
-        <v>4.33113694190979</v>
+        <v>4.737416505813599</v>
       </c>
       <c r="D36" t="n">
-        <v>5.021114587783813</v>
+        <v>4.016752004623413</v>
       </c>
       <c r="E36" t="n">
-        <v>4.317947387695312</v>
+        <v>4.1848304271698</v>
       </c>
       <c r="F36" t="n">
-        <v>4.014380216598511</v>
+        <v>5.218698740005493</v>
       </c>
       <c r="G36" t="n">
-        <v>4.586106777191162</v>
+        <v>5.155860424041748</v>
       </c>
       <c r="H36" t="n">
-        <v>4.349994421005249</v>
+        <v>4.243206024169922</v>
       </c>
       <c r="I36" t="n">
-        <v>3.78947377204895</v>
+        <v>4.214252233505249</v>
       </c>
       <c r="J36" t="n">
-        <v>3.743005990982056</v>
+        <v>5.380268335342407</v>
       </c>
       <c r="K36" t="n">
-        <v>4.184644460678101</v>
+        <v>4.258140802383423</v>
       </c>
       <c r="L36" t="n">
-        <v>4.240480256080628</v>
+        <v>4.556133127212524</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>4.620441198348999</v>
+        <v>4.907995223999023</v>
       </c>
       <c r="C37" t="n">
-        <v>4.908179998397827</v>
+        <v>4.768332004547119</v>
       </c>
       <c r="D37" t="n">
-        <v>4.780835151672363</v>
+        <v>5.107485055923462</v>
       </c>
       <c r="E37" t="n">
-        <v>4.354423522949219</v>
+        <v>5.789237260818481</v>
       </c>
       <c r="F37" t="n">
-        <v>5.037437200546265</v>
+        <v>5.743860960006714</v>
       </c>
       <c r="G37" t="n">
-        <v>5.250783443450928</v>
+        <v>5.578787088394165</v>
       </c>
       <c r="H37" t="n">
-        <v>4.613096237182617</v>
+        <v>5.57978892326355</v>
       </c>
       <c r="I37" t="n">
-        <v>4.718212127685547</v>
+        <v>4.810725927352905</v>
       </c>
       <c r="J37" t="n">
-        <v>5.3963303565979</v>
+        <v>5.091013669967651</v>
       </c>
       <c r="K37" t="n">
-        <v>4.357109546661377</v>
+        <v>4.865088701248169</v>
       </c>
       <c r="L37" t="n">
-        <v>4.803684878349304</v>
+        <v>5.224231481552124</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>3.689603805541992</v>
+        <v>4.118001937866211</v>
       </c>
       <c r="C38" t="n">
-        <v>3.793256521224976</v>
+        <v>3.91948676109314</v>
       </c>
       <c r="D38" t="n">
-        <v>3.993676424026489</v>
+        <v>3.843700647354126</v>
       </c>
       <c r="E38" t="n">
-        <v>4.135016679763794</v>
+        <v>4.545889139175415</v>
       </c>
       <c r="F38" t="n">
-        <v>3.847839593887329</v>
+        <v>4.127011060714722</v>
       </c>
       <c r="G38" t="n">
-        <v>3.838793039321899</v>
+        <v>4.854126930236816</v>
       </c>
       <c r="H38" t="n">
-        <v>3.603647470474243</v>
+        <v>3.912530899047852</v>
       </c>
       <c r="I38" t="n">
-        <v>3.72852087020874</v>
+        <v>4.152896881103516</v>
       </c>
       <c r="J38" t="n">
-        <v>3.777073860168457</v>
+        <v>4.186347723007202</v>
       </c>
       <c r="K38" t="n">
-        <v>3.777966976165771</v>
+        <v>3.768392086029053</v>
       </c>
       <c r="L38" t="n">
-        <v>3.818539524078369</v>
+        <v>4.142838406562805</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>4.227541208267212</v>
+        <v>4.131964683532715</v>
       </c>
       <c r="C39" t="n">
-        <v>4.392858266830444</v>
+        <v>4.363871335983276</v>
       </c>
       <c r="D39" t="n">
-        <v>4.20056676864624</v>
+        <v>5.221790075302124</v>
       </c>
       <c r="E39" t="n">
-        <v>4.233289957046509</v>
+        <v>4.442666530609131</v>
       </c>
       <c r="F39" t="n">
-        <v>4.087215185165405</v>
+        <v>4.278590440750122</v>
       </c>
       <c r="G39" t="n">
-        <v>5.163828611373901</v>
+        <v>4.052667140960693</v>
       </c>
       <c r="H39" t="n">
-        <v>4.499446868896484</v>
+        <v>4.516001224517822</v>
       </c>
       <c r="I39" t="n">
-        <v>5.196713447570801</v>
+        <v>4.339961051940918</v>
       </c>
       <c r="J39" t="n">
-        <v>4.289974927902222</v>
+        <v>4.454655885696411</v>
       </c>
       <c r="K39" t="n">
-        <v>4.167913913726807</v>
+        <v>4.818737268447876</v>
       </c>
       <c r="L39" t="n">
-        <v>4.445934915542603</v>
+        <v>4.462090563774109</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>4.25567889213562</v>
+        <v>4.583328723907471</v>
       </c>
       <c r="C40" t="n">
-        <v>4.274348974227905</v>
+        <v>4.53993034362793</v>
       </c>
       <c r="D40" t="n">
-        <v>4.498111724853516</v>
+        <v>4.713493347167969</v>
       </c>
       <c r="E40" t="n">
-        <v>4.223102569580078</v>
+        <v>4.548397779464722</v>
       </c>
       <c r="F40" t="n">
-        <v>4.47526741027832</v>
+        <v>4.388322353363037</v>
       </c>
       <c r="G40" t="n">
-        <v>4.254418134689331</v>
+        <v>4.51250696182251</v>
       </c>
       <c r="H40" t="n">
-        <v>4.611218690872192</v>
+        <v>5.031186819076538</v>
       </c>
       <c r="I40" t="n">
-        <v>4.458654403686523</v>
+        <v>4.574838399887085</v>
       </c>
       <c r="J40" t="n">
-        <v>4.606350898742676</v>
+        <v>4.931430339813232</v>
       </c>
       <c r="K40" t="n">
-        <v>4.711971998214722</v>
+        <v>5.032169342041016</v>
       </c>
       <c r="L40" t="n">
-        <v>4.436912369728089</v>
+        <v>4.685560441017151</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>4.778985500335693</v>
+        <v>4.918040990829468</v>
       </c>
       <c r="C41" t="n">
-        <v>4.754925727844238</v>
+        <v>4.87982177734375</v>
       </c>
       <c r="D41" t="n">
-        <v>4.189358711242676</v>
+        <v>4.566614627838135</v>
       </c>
       <c r="E41" t="n">
-        <v>4.106353521347046</v>
+        <v>4.580065011978149</v>
       </c>
       <c r="F41" t="n">
-        <v>3.954325437545776</v>
+        <v>4.430476903915405</v>
       </c>
       <c r="G41" t="n">
-        <v>4.35886025428772</v>
+        <v>4.828451633453369</v>
       </c>
       <c r="H41" t="n">
-        <v>4.359041929244995</v>
+        <v>4.733673334121704</v>
       </c>
       <c r="I41" t="n">
-        <v>4.184467077255249</v>
+        <v>4.864330291748047</v>
       </c>
       <c r="J41" t="n">
-        <v>4.259037971496582</v>
+        <v>4.657398700714111</v>
       </c>
       <c r="K41" t="n">
-        <v>4.824571371078491</v>
+        <v>4.840228080749512</v>
       </c>
       <c r="L41" t="n">
-        <v>4.376992750167847</v>
+        <v>4.729910135269165</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>5.148350238800049</v>
+        <v>4.837691068649292</v>
       </c>
       <c r="C42" t="n">
-        <v>4.587566137313843</v>
+        <v>4.94538950920105</v>
       </c>
       <c r="D42" t="n">
-        <v>4.44242262840271</v>
+        <v>4.623203992843628</v>
       </c>
       <c r="E42" t="n">
-        <v>4.611247062683105</v>
+        <v>4.956857442855835</v>
       </c>
       <c r="F42" t="n">
-        <v>4.880594253540039</v>
+        <v>5.27306604385376</v>
       </c>
       <c r="G42" t="n">
-        <v>4.859525203704834</v>
+        <v>5.286025285720825</v>
       </c>
       <c r="H42" t="n">
-        <v>4.01989221572876</v>
+        <v>4.786276578903198</v>
       </c>
       <c r="I42" t="n">
-        <v>4.397202968597412</v>
+        <v>4.560389041900635</v>
       </c>
       <c r="J42" t="n">
-        <v>4.946443319320679</v>
+        <v>4.890021085739136</v>
       </c>
       <c r="K42" t="n">
-        <v>4.40825629234314</v>
+        <v>5.273538827896118</v>
       </c>
       <c r="L42" t="n">
-        <v>4.630150032043457</v>
+        <v>4.943245887756348</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>4.323875188827515</v>
+        <v>6.352814674377441</v>
       </c>
       <c r="C43" t="n">
-        <v>5.467330694198608</v>
+        <v>5.429167509078979</v>
       </c>
       <c r="D43" t="n">
-        <v>4.368263483047485</v>
+        <v>5.099506139755249</v>
       </c>
       <c r="E43" t="n">
-        <v>4.699890613555908</v>
+        <v>4.379330396652222</v>
       </c>
       <c r="F43" t="n">
-        <v>4.334349870681763</v>
+        <v>5.013750791549683</v>
       </c>
       <c r="G43" t="n">
-        <v>4.560829877853394</v>
+        <v>4.506528854370117</v>
       </c>
       <c r="H43" t="n">
-        <v>4.363988399505615</v>
+        <v>5.268066883087158</v>
       </c>
       <c r="I43" t="n">
-        <v>4.872438430786133</v>
+        <v>4.89302134513855</v>
       </c>
       <c r="J43" t="n">
-        <v>4.276430368423462</v>
+        <v>4.935894250869751</v>
       </c>
       <c r="K43" t="n">
-        <v>4.660944700241089</v>
+        <v>4.8476722240448</v>
       </c>
       <c r="L43" t="n">
-        <v>4.592834162712097</v>
+        <v>5.072575306892395</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>4.402580738067627</v>
+        <v>4.974801063537598</v>
       </c>
       <c r="C44" t="n">
-        <v>4.630262851715088</v>
+        <v>4.971314668655396</v>
       </c>
       <c r="D44" t="n">
-        <v>4.513919115066528</v>
+        <v>4.773326635360718</v>
       </c>
       <c r="E44" t="n">
-        <v>4.514941453933716</v>
+        <v>4.547892093658447</v>
       </c>
       <c r="F44" t="n">
-        <v>4.067466974258423</v>
+        <v>4.816726922988892</v>
       </c>
       <c r="G44" t="n">
-        <v>4.375547647476196</v>
+        <v>4.7788245677948</v>
       </c>
       <c r="H44" t="n">
-        <v>4.329071283340454</v>
+        <v>4.357383251190186</v>
       </c>
       <c r="I44" t="n">
-        <v>4.631556034088135</v>
+        <v>4.343425273895264</v>
       </c>
       <c r="J44" t="n">
-        <v>4.049047231674194</v>
+        <v>4.784814834594727</v>
       </c>
       <c r="K44" t="n">
-        <v>4.353751659393311</v>
+        <v>4.190618753433228</v>
       </c>
       <c r="L44" t="n">
-        <v>4.386814498901368</v>
+        <v>4.653912806510926</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>3.642848014831543</v>
+        <v>4.019531726837158</v>
       </c>
       <c r="C45" t="n">
-        <v>4.204386949539185</v>
+        <v>4.23052191734314</v>
       </c>
       <c r="D45" t="n">
-        <v>4.078968286514282</v>
+        <v>4.451438665390015</v>
       </c>
       <c r="E45" t="n">
-        <v>3.968992471694946</v>
+        <v>4.82948899269104</v>
       </c>
       <c r="F45" t="n">
-        <v>3.813586711883545</v>
+        <v>4.817506313323975</v>
       </c>
       <c r="G45" t="n">
-        <v>3.973546266555786</v>
+        <v>4.216086864471436</v>
       </c>
       <c r="H45" t="n">
-        <v>4.423031568527222</v>
+        <v>4.421499490737915</v>
       </c>
       <c r="I45" t="n">
-        <v>3.889852046966553</v>
+        <v>4.06142783164978</v>
       </c>
       <c r="J45" t="n">
-        <v>4.273427486419678</v>
+        <v>4.136730670928955</v>
       </c>
       <c r="K45" t="n">
-        <v>4.400108098983765</v>
+        <v>4.287330627441406</v>
       </c>
       <c r="L45" t="n">
-        <v>4.06687479019165</v>
+        <v>4.347156310081482</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>4.029807806015015</v>
+        <v>4.898744821548462</v>
       </c>
       <c r="C46" t="n">
-        <v>4.094185829162598</v>
+        <v>4.471858739852905</v>
       </c>
       <c r="D46" t="n">
-        <v>3.9676513671875</v>
+        <v>4.369128942489624</v>
       </c>
       <c r="E46" t="n">
-        <v>4.131203889846802</v>
+        <v>4.308300256729126</v>
       </c>
       <c r="F46" t="n">
-        <v>3.968178987503052</v>
+        <v>4.343693494796753</v>
       </c>
       <c r="G46" t="n">
-        <v>4.09731912612915</v>
+        <v>4.537684440612793</v>
       </c>
       <c r="H46" t="n">
-        <v>4.440847158432007</v>
+        <v>4.569096326828003</v>
       </c>
       <c r="I46" t="n">
-        <v>4.736435413360596</v>
+        <v>4.75710654258728</v>
       </c>
       <c r="J46" t="n">
-        <v>4.049538850784302</v>
+        <v>4.502780199050903</v>
       </c>
       <c r="K46" t="n">
-        <v>4.233025789260864</v>
+        <v>4.565619707107544</v>
       </c>
       <c r="L46" t="n">
-        <v>4.174819421768189</v>
+        <v>4.53240134716034</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>3.593440055847168</v>
+        <v>3.827038288116455</v>
       </c>
       <c r="C47" t="n">
-        <v>3.737457990646362</v>
+        <v>3.774172306060791</v>
       </c>
       <c r="D47" t="n">
-        <v>3.649328231811523</v>
+        <v>3.981135606765747</v>
       </c>
       <c r="E47" t="n">
-        <v>3.610995292663574</v>
+        <v>3.757211446762085</v>
       </c>
       <c r="F47" t="n">
-        <v>3.999932527542114</v>
+        <v>3.516346216201782</v>
       </c>
       <c r="G47" t="n">
-        <v>3.969665765762329</v>
+        <v>3.889405965805054</v>
       </c>
       <c r="H47" t="n">
-        <v>4.082581758499146</v>
+        <v>4.056462287902832</v>
       </c>
       <c r="I47" t="n">
-        <v>3.469718933105469</v>
+        <v>4.08687162399292</v>
       </c>
       <c r="J47" t="n">
-        <v>3.479976892471313</v>
+        <v>3.758722066879272</v>
       </c>
       <c r="K47" t="n">
-        <v>3.372639656066895</v>
+        <v>4.691277503967285</v>
       </c>
       <c r="L47" t="n">
-        <v>3.696573710441589</v>
+        <v>3.933864331245422</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>4.699678659439087</v>
+        <v>4.930654525756836</v>
       </c>
       <c r="C48" t="n">
-        <v>4.634131908416748</v>
+        <v>4.760098695755005</v>
       </c>
       <c r="D48" t="n">
-        <v>4.434171199798584</v>
+        <v>5.010948657989502</v>
       </c>
       <c r="E48" t="n">
-        <v>4.620248556137085</v>
+        <v>5.525457143783569</v>
       </c>
       <c r="F48" t="n">
-        <v>4.364446401596069</v>
+        <v>4.918962240219116</v>
       </c>
       <c r="G48" t="n">
-        <v>4.622629404067993</v>
+        <v>5.692038536071777</v>
       </c>
       <c r="H48" t="n">
-        <v>4.216722249984741</v>
+        <v>5.321766138076782</v>
       </c>
       <c r="I48" t="n">
-        <v>5.013668060302734</v>
+        <v>4.817450284957886</v>
       </c>
       <c r="J48" t="n">
-        <v>4.254058837890625</v>
+        <v>5.458310604095459</v>
       </c>
       <c r="K48" t="n">
-        <v>5.172225952148438</v>
+        <v>4.889781951904297</v>
       </c>
       <c r="L48" t="n">
-        <v>4.603198122978211</v>
+        <v>5.132546877861023</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>5.030810117721558</v>
+        <v>4.462396860122681</v>
       </c>
       <c r="C49" t="n">
-        <v>4.628315448760986</v>
+        <v>4.228985548019409</v>
       </c>
       <c r="D49" t="n">
-        <v>4.434847831726074</v>
+        <v>4.781560659408569</v>
       </c>
       <c r="E49" t="n">
-        <v>4.937912940979004</v>
+        <v>4.690277576446533</v>
       </c>
       <c r="F49" t="n">
-        <v>4.551002264022827</v>
+        <v>4.805480241775513</v>
       </c>
       <c r="G49" t="n">
-        <v>4.532617092132568</v>
+        <v>5.400935173034668</v>
       </c>
       <c r="H49" t="n">
-        <v>4.589456796646118</v>
+        <v>4.436445951461792</v>
       </c>
       <c r="I49" t="n">
-        <v>4.175939798355103</v>
+        <v>4.841423511505127</v>
       </c>
       <c r="J49" t="n">
-        <v>4.335593461990356</v>
+        <v>4.459942817687988</v>
       </c>
       <c r="K49" t="n">
-        <v>4.154521226882935</v>
+        <v>5.275247812271118</v>
       </c>
       <c r="L49" t="n">
-        <v>4.537101697921753</v>
+        <v>4.73826961517334</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>3.899064540863037</v>
+        <v>5.105236291885376</v>
       </c>
       <c r="C50" t="n">
-        <v>4.258524656295776</v>
+        <v>3.894866704940796</v>
       </c>
       <c r="D50" t="n">
-        <v>3.973534345626831</v>
+        <v>4.0319983959198</v>
       </c>
       <c r="E50" t="n">
-        <v>3.922693014144897</v>
+        <v>4.070394039154053</v>
       </c>
       <c r="F50" t="n">
-        <v>4.289660215377808</v>
+        <v>3.9636390209198</v>
       </c>
       <c r="G50" t="n">
-        <v>3.740486621856689</v>
+        <v>4.348183155059814</v>
       </c>
       <c r="H50" t="n">
-        <v>4.197947263717651</v>
+        <v>4.902738094329834</v>
       </c>
       <c r="I50" t="n">
-        <v>4.42762303352356</v>
+        <v>4.404524087905884</v>
       </c>
       <c r="J50" t="n">
-        <v>4.346951723098755</v>
+        <v>3.929269552230835</v>
       </c>
       <c r="K50" t="n">
-        <v>4.415604829788208</v>
+        <v>4.140237092971802</v>
       </c>
       <c r="L50" t="n">
-        <v>4.147209024429321</v>
+        <v>4.279108643531799</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>4.517781019210815</v>
+        <v>4.884775638580322</v>
       </c>
       <c r="C51" t="n">
-        <v>4.974819898605347</v>
+        <v>4.8254554271698</v>
       </c>
       <c r="D51" t="n">
-        <v>4.682151556015015</v>
+        <v>4.389584064483643</v>
       </c>
       <c r="E51" t="n">
-        <v>4.199070930480957</v>
+        <v>4.373108386993408</v>
       </c>
       <c r="F51" t="n">
-        <v>5.085177898406982</v>
+        <v>5.007063150405884</v>
       </c>
       <c r="G51" t="n">
-        <v>4.314873933792114</v>
+        <v>4.850876092910767</v>
       </c>
       <c r="H51" t="n">
-        <v>4.416929006576538</v>
+        <v>4.618968486785889</v>
       </c>
       <c r="I51" t="n">
-        <v>3.986197948455811</v>
+        <v>4.146703243255615</v>
       </c>
       <c r="J51" t="n">
-        <v>4.162744045257568</v>
+        <v>4.442422151565552</v>
       </c>
       <c r="K51" t="n">
-        <v>4.165380477905273</v>
+        <v>5.253917932510376</v>
       </c>
       <c r="L51" t="n">
-        <v>4.450512671470642</v>
+        <v>4.679287457466126</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4.336694202423096</v>
+        <v>4.683117070198059</v>
       </c>
       <c r="C52" t="n">
-        <v>4.342016258239746</v>
+        <v>4.648696808815003</v>
       </c>
       <c r="D52" t="n">
-        <v>4.292413468360901</v>
+        <v>4.633458824157715</v>
       </c>
       <c r="E52" t="n">
-        <v>4.330174798965454</v>
+        <v>4.57821494102478</v>
       </c>
       <c r="F52" t="n">
-        <v>4.287164087295532</v>
+        <v>4.625936250686646</v>
       </c>
       <c r="G52" t="n">
-        <v>4.406376180648803</v>
+        <v>4.676844754219055</v>
       </c>
       <c r="H52" t="n">
-        <v>4.24587833404541</v>
+        <v>4.670703973770141</v>
       </c>
       <c r="I52" t="n">
-        <v>4.389417419433594</v>
+        <v>4.72241674900055</v>
       </c>
       <c r="J52" t="n">
-        <v>4.300805234909058</v>
+        <v>4.596060461997986</v>
       </c>
       <c r="K52" t="n">
-        <v>4.29466543674469</v>
+        <v>4.709121608734131</v>
       </c>
       <c r="L52" t="n">
-        <v>4.322560542106628</v>
+        <v>4.654457144260406</v>
       </c>
     </row>
   </sheetData>
